--- a/_ForDRA/BVSimulationFiles/102.xlsx
+++ b/_ForDRA/BVSimulationFiles/102.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plot-data (4)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plot-data (3)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="1">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -24,316 +24,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C5700"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -341,204 +41,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.3999755851924192"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Title" xfId="1" builtinId="15"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
-    <cellStyle name="Input" xfId="9" builtinId="20"/>
-    <cellStyle name="Output" xfId="10" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="Note" xfId="15" builtinId="10"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
-    <cellStyle name="Total" xfId="17" builtinId="25"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -933,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,13 +476,13 @@
         <v>0.005263157894736842</v>
       </c>
       <c r="K1" t="n">
-        <v>0.005921052631578948</v>
+        <v>0.005921052631578947</v>
       </c>
       <c r="L1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="M1" t="n">
-        <v>0.007236842105263158</v>
+        <v>0.007236842105263157</v>
       </c>
       <c r="N1" t="n">
         <v>0.007894736842105263</v>
@@ -992,7 +503,7 @@
         <v>0.01118421052631579</v>
       </c>
       <c r="T1" t="n">
-        <v>0.0118421052631579</v>
+        <v>0.01184210526315789</v>
       </c>
       <c r="U1" t="n">
         <v>0.0125</v>
@@ -1003,3574 +514,2989 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.625356853471145e-08</v>
+        <v>0.1296609764097694</v>
       </c>
       <c r="C2" t="n">
-        <v>1.640312030311324e-08</v>
+        <v>0.1308540084675217</v>
       </c>
       <c r="D2" t="n">
-        <v>1.65540481220349e-08</v>
+        <v>0.1320580178102692</v>
       </c>
       <c r="E2" t="n">
-        <v>1.670636465274454e-08</v>
+        <v>0.1332731054418242</v>
       </c>
       <c r="F2" t="n">
-        <v>1.686008267300865e-08</v>
+        <v>0.1344993732953517</v>
       </c>
       <c r="G2" t="n">
-        <v>1.701521507816411e-08</v>
+        <v>0.1357369242419204</v>
       </c>
       <c r="H2" t="n">
-        <v>1.717177488219986e-08</v>
+        <v>0.1369858620991329</v>
       </c>
       <c r="I2" t="n">
-        <v>1.732977521884876e-08</v>
+        <v>0.1382462916398345</v>
       </c>
       <c r="J2" t="n">
-        <v>1.748922934268929e-08</v>
+        <v>0.1395183186009029</v>
       </c>
       <c r="K2" t="n">
-        <v>1.765015063025747e-08</v>
+        <v>0.1408020496921183</v>
       </c>
       <c r="L2" t="n">
-        <v>1.78125525811691e-08</v>
+        <v>0.142097592605115</v>
       </c>
       <c r="M2" t="n">
-        <v>1.797644881925211e-08</v>
+        <v>0.1434050560224161</v>
       </c>
       <c r="N2" t="n">
-        <v>1.814185309368955e-08</v>
+        <v>0.1447245496265503</v>
       </c>
       <c r="O2" t="n">
-        <v>1.8308779280173e-08</v>
+        <v>0.1460561841092536</v>
       </c>
       <c r="P2" t="n">
-        <v>1.847724138206652e-08</v>
+        <v>0.1474000711807547</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.864725353158146e-08</v>
+        <v>0.1487563235791467</v>
       </c>
       <c r="R2" t="n">
-        <v>1.881882999096198e-08</v>
+        <v>0.1501250550798444</v>
       </c>
       <c r="S2" t="n">
-        <v>1.899198515368151e-08</v>
+        <v>0.1515063805051292</v>
       </c>
       <c r="T2" t="n">
-        <v>1.916673354565019e-08</v>
+        <v>0.1529004157337811</v>
       </c>
       <c r="U2" t="n">
-        <v>1.934308982643346e-08</v>
+        <v>0.1543072777108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01493854748603347</v>
+        <v>0.01993358633776079</v>
       </c>
       <c r="B3" t="n">
-        <v>1.625356853471145e-08</v>
+        <v>0.1234122546550811</v>
       </c>
       <c r="C3" t="n">
-        <v>1.640312030311324e-08</v>
+        <v>0.1245477911919778</v>
       </c>
       <c r="D3" t="n">
-        <v>1.65540481220349e-08</v>
+        <v>0.1256937759880869</v>
       </c>
       <c r="E3" t="n">
-        <v>1.670636465274454e-08</v>
+        <v>0.126850305179567</v>
       </c>
       <c r="F3" t="n">
-        <v>1.686008267300865e-08</v>
+        <v>0.1280174757871413</v>
       </c>
       <c r="G3" t="n">
-        <v>1.701521507816411e-08</v>
+        <v>0.1291953857242368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.717177488219986e-08</v>
+        <v>0.1303841338051981</v>
       </c>
       <c r="I3" t="n">
-        <v>1.732977521884876e-08</v>
+        <v>0.1315838197535767</v>
       </c>
       <c r="J3" t="n">
-        <v>1.748922934268929e-08</v>
+        <v>0.1327945442104973</v>
       </c>
       <c r="K3" t="n">
-        <v>1.765015063025747e-08</v>
+        <v>0.1340164087430998</v>
       </c>
       <c r="L3" t="n">
-        <v>1.78125525811691e-08</v>
+        <v>0.1352495158530606</v>
       </c>
       <c r="M3" t="n">
-        <v>1.797644881925211e-08</v>
+        <v>0.1364939689851905</v>
       </c>
       <c r="N3" t="n">
-        <v>1.814185309368955e-08</v>
+        <v>0.1377498725361134</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8308779280173e-08</v>
+        <v>0.1390173318630238</v>
       </c>
       <c r="P3" t="n">
-        <v>1.847724138206652e-08</v>
+        <v>0.1402964532925248</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.864725353158146e-08</v>
+        <v>0.1415873441295485</v>
       </c>
       <c r="R3" t="n">
-        <v>1.881882999096198e-08</v>
+        <v>0.1428901126663572</v>
       </c>
       <c r="S3" t="n">
-        <v>1.899198515368151e-08</v>
+        <v>0.1442048681916283</v>
       </c>
       <c r="T3" t="n">
-        <v>1.916673354565019e-08</v>
+        <v>0.1455317209996222</v>
       </c>
       <c r="U3" t="n">
-        <v>1.934308982643346e-08</v>
+        <v>0.1468707823994353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03521229050279321</v>
+        <v>0.04439753320683112</v>
       </c>
       <c r="B4" t="n">
-        <v>1.509259935366066e-08</v>
+        <v>0.1140391720230495</v>
       </c>
       <c r="C4" t="n">
-        <v>1.523146885289089e-08</v>
+        <v>0.1150884652786629</v>
       </c>
       <c r="D4" t="n">
-        <v>1.537161611331815e-08</v>
+        <v>0.1161474132548143</v>
       </c>
       <c r="E4" t="n">
-        <v>1.551305289183424e-08</v>
+        <v>0.117216104786182</v>
       </c>
       <c r="F4" t="n">
-        <v>1.565579105350806e-08</v>
+        <v>0.1182946295248267</v>
       </c>
       <c r="G4" t="n">
-        <v>1.579984257258098e-08</v>
+        <v>0.1193830779477124</v>
       </c>
       <c r="H4" t="n">
-        <v>1.594521953347133e-08</v>
+        <v>0.1204815413642968</v>
       </c>
       <c r="I4" t="n">
-        <v>1.609193413178816e-08</v>
+        <v>0.121590111924191</v>
       </c>
       <c r="J4" t="n">
-        <v>1.623999867535436e-08</v>
+        <v>0.1227088826248898</v>
       </c>
       <c r="K4" t="n">
-        <v>1.638942558523911e-08</v>
+        <v>0.1238379473195731</v>
       </c>
       <c r="L4" t="n">
-        <v>1.65402273967999e-08</v>
+        <v>0.1249774007249799</v>
       </c>
       <c r="M4" t="n">
-        <v>1.669241676073413e-08</v>
+        <v>0.1261273384293531</v>
       </c>
       <c r="N4" t="n">
-        <v>1.684600644414033e-08</v>
+        <v>0.1272878569004591</v>
       </c>
       <c r="O4" t="n">
-        <v>1.700100933158925e-08</v>
+        <v>0.1284590534936801</v>
       </c>
       <c r="P4" t="n">
-        <v>1.715743842620465e-08</v>
+        <v>0.129641026460181</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.731530685075424e-08</v>
+        <v>0.1308338749551523</v>
       </c>
       <c r="R4" t="n">
-        <v>1.747462784875044e-08</v>
+        <v>0.1320376990461274</v>
       </c>
       <c r="S4" t="n">
-        <v>1.763541478556143e-08</v>
+        <v>0.1332525997213779</v>
       </c>
       <c r="T4" t="n">
-        <v>1.779768114953234e-08</v>
+        <v>0.134478678898385</v>
       </c>
       <c r="U4" t="n">
-        <v>1.796144055311681e-08</v>
+        <v>0.1357160394323895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0554860335195531</v>
+        <v>0.06161290322580635</v>
       </c>
       <c r="B5" t="n">
-        <v>1.462821168124032e-08</v>
+        <v>0.1109148111457062</v>
       </c>
       <c r="C5" t="n">
-        <v>1.476280827280193e-08</v>
+        <v>0.1119353566408919</v>
       </c>
       <c r="D5" t="n">
-        <v>1.489864330983142e-08</v>
+        <v>0.1129652923437241</v>
       </c>
       <c r="E5" t="n">
-        <v>1.50357281874701e-08</v>
+        <v>0.1140047046550543</v>
       </c>
       <c r="F5" t="n">
-        <v>1.51740744057078e-08</v>
+        <v>0.1150536807707224</v>
       </c>
       <c r="G5" t="n">
-        <v>1.531369357034771e-08</v>
+        <v>0.1161123086888715</v>
       </c>
       <c r="H5" t="n">
-        <v>1.545459739397989e-08</v>
+        <v>0.1171806772173304</v>
       </c>
       <c r="I5" t="n">
-        <v>1.55967976969639e-08</v>
+        <v>0.1182588759810631</v>
       </c>
       <c r="J5" t="n">
-        <v>1.574030640842037e-08</v>
+        <v>0.1193469954296879</v>
       </c>
       <c r="K5" t="n">
-        <v>1.588513556723174e-08</v>
+        <v>0.1204451268450649</v>
       </c>
       <c r="L5" t="n">
-        <v>1.60312973230522e-08</v>
+        <v>0.1215533623489536</v>
       </c>
       <c r="M5" t="n">
-        <v>1.617880393732691e-08</v>
+        <v>0.1226717949107413</v>
       </c>
       <c r="N5" t="n">
-        <v>1.632766778432061e-08</v>
+        <v>0.1238005183552417</v>
       </c>
       <c r="O5" t="n">
-        <v>1.647790135215572e-08</v>
+        <v>0.1249396273705662</v>
       </c>
       <c r="P5" t="n">
-        <v>1.662951724385988e-08</v>
+        <v>0.1260892175160671</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.678252817842333e-08</v>
+        <v>0.1272493852303542</v>
       </c>
       <c r="R5" t="n">
-        <v>1.693694699186579e-08</v>
+        <v>0.1284202278393848</v>
       </c>
       <c r="S5" t="n">
-        <v>1.709278663831337e-08</v>
+        <v>0.1296018435646284</v>
       </c>
       <c r="T5" t="n">
-        <v>1.725006019108518e-08</v>
+        <v>0.1307943315313065</v>
       </c>
       <c r="U5" t="n">
-        <v>1.740878084379012e-08</v>
+        <v>0.1319977917767082</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.07896089385474861</v>
+        <v>0.08064041745730549</v>
       </c>
       <c r="B6" t="n">
-        <v>1.369943633639964e-08</v>
+        <v>0.1077904502683621</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3825487112624e-08</v>
+        <v>0.1087822480031199</v>
       </c>
       <c r="D6" t="n">
-        <v>1.395269770285797e-08</v>
+        <v>0.1097831714326329</v>
       </c>
       <c r="E6" t="n">
-        <v>1.408107877874181e-08</v>
+        <v>0.1107933045239257</v>
       </c>
       <c r="F6" t="n">
-        <v>1.421064111010728e-08</v>
+        <v>0.1118127320166172</v>
       </c>
       <c r="G6" t="n">
-        <v>1.434139556588116e-08</v>
+        <v>0.1128415394300297</v>
       </c>
       <c r="H6" t="n">
-        <v>1.447335311499701e-08</v>
+        <v>0.113879813070363</v>
       </c>
       <c r="I6" t="n">
-        <v>1.460652482731537e-08</v>
+        <v>0.1149276400379342</v>
       </c>
       <c r="J6" t="n">
-        <v>1.474092187455238e-08</v>
+        <v>0.115985108234485</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4876555531217e-08</v>
+        <v>0.1170523063705556</v>
       </c>
       <c r="L6" t="n">
-        <v>1.501343717555679e-08</v>
+        <v>0.1181293239729264</v>
       </c>
       <c r="M6" t="n">
-        <v>1.515157829051247e-08</v>
+        <v>0.1192162513921285</v>
       </c>
       <c r="N6" t="n">
-        <v>1.529099046468118e-08</v>
+        <v>0.1203131798100232</v>
       </c>
       <c r="O6" t="n">
-        <v>1.543168539328866e-08</v>
+        <v>0.1214202012474513</v>
       </c>
       <c r="P6" t="n">
-        <v>1.557367487917033e-08</v>
+        <v>0.1225374085719522</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57169708337615e-08</v>
+        <v>0.1236648955055551</v>
       </c>
       <c r="R6" t="n">
-        <v>1.586158527809651e-08</v>
+        <v>0.1248027566326412</v>
       </c>
       <c r="S6" t="n">
-        <v>1.600753034381725e-08</v>
+        <v>0.125951087407878</v>
       </c>
       <c r="T6" t="n">
-        <v>1.615481827419085e-08</v>
+        <v>0.1271099841642271</v>
       </c>
       <c r="U6" t="n">
-        <v>1.630346142513675e-08</v>
+        <v>0.1282795441210259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1035027932960894</v>
+        <v>0.09876185958254273</v>
       </c>
       <c r="B7" t="n">
-        <v>1.32350486639793e-08</v>
+        <v>0.1031039089523467</v>
       </c>
       <c r="C7" t="n">
-        <v>1.335682653253504e-08</v>
+        <v>0.1040525850464629</v>
       </c>
       <c r="D7" t="n">
-        <v>1.347972489937125e-08</v>
+        <v>0.1050099900659971</v>
       </c>
       <c r="E7" t="n">
-        <v>1.360375407437767e-08</v>
+        <v>0.1059762043272336</v>
       </c>
       <c r="F7" t="n">
-        <v>1.372892446230702e-08</v>
+        <v>0.1069513088854603</v>
       </c>
       <c r="G7" t="n">
-        <v>1.385524656364789e-08</v>
+        <v>0.1079353855417679</v>
       </c>
       <c r="H7" t="n">
-        <v>1.398273097550558e-08</v>
+        <v>0.1089285168499128</v>
       </c>
       <c r="I7" t="n">
-        <v>1.411138839249111e-08</v>
+        <v>0.1099307861232418</v>
       </c>
       <c r="J7" t="n">
-        <v>1.424122960761839e-08</v>
+        <v>0.1109422774416818</v>
       </c>
       <c r="K7" t="n">
-        <v>1.437226551320963e-08</v>
+        <v>0.1119630756587928</v>
       </c>
       <c r="L7" t="n">
-        <v>1.450450710180909e-08</v>
+        <v>0.1129932664088865</v>
       </c>
       <c r="M7" t="n">
-        <v>1.463796546710526e-08</v>
+        <v>0.1140329361142103</v>
       </c>
       <c r="N7" t="n">
-        <v>1.477265180486146e-08</v>
+        <v>0.1150821719921966</v>
       </c>
       <c r="O7" t="n">
-        <v>1.490857741385513e-08</v>
+        <v>0.1161410620627799</v>
       </c>
       <c r="P7" t="n">
-        <v>1.504575369682556e-08</v>
+        <v>0.1172096951557808</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.518419216143059e-08</v>
+        <v>0.1182881609183575</v>
       </c>
       <c r="R7" t="n">
-        <v>1.532390442121186e-08</v>
+        <v>0.1193765498225268</v>
       </c>
       <c r="S7" t="n">
-        <v>1.546490219656919e-08</v>
+        <v>0.1204749531727533</v>
       </c>
       <c r="T7" t="n">
-        <v>1.560719731574369e-08</v>
+        <v>0.121583463113609</v>
       </c>
       <c r="U7" t="n">
-        <v>1.575080171581007e-08</v>
+        <v>0.1227021726375035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1248435754189945</v>
+        <v>0.1168833017077798</v>
       </c>
       <c r="B8" t="n">
-        <v>1.277066099155896e-08</v>
+        <v>0.09997954807500255</v>
       </c>
       <c r="C8" t="n">
-        <v>1.288816595244608e-08</v>
+        <v>0.100899476408691</v>
       </c>
       <c r="D8" t="n">
-        <v>1.300675209588453e-08</v>
+        <v>0.101827869154906</v>
       </c>
       <c r="E8" t="n">
-        <v>1.312642937001352e-08</v>
+        <v>0.102764804196105</v>
       </c>
       <c r="F8" t="n">
-        <v>1.324720781450676e-08</v>
+        <v>0.1037103601313551</v>
       </c>
       <c r="G8" t="n">
-        <v>1.336909756141461e-08</v>
+        <v>0.1046646162829262</v>
       </c>
       <c r="H8" t="n">
-        <v>1.349210883601414e-08</v>
+        <v>0.1056276527029454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.361625195766685e-08</v>
+        <v>0.106599550180113</v>
       </c>
       <c r="J8" t="n">
-        <v>1.37415373406844e-08</v>
+        <v>0.1075803902464789</v>
       </c>
       <c r="K8" t="n">
-        <v>1.386797549520226e-08</v>
+        <v>0.1085702551842836</v>
       </c>
       <c r="L8" t="n">
-        <v>1.399557702806139e-08</v>
+        <v>0.1095692280328593</v>
       </c>
       <c r="M8" t="n">
-        <v>1.412435264369804e-08</v>
+        <v>0.1105773925955975</v>
       </c>
       <c r="N8" t="n">
-        <v>1.425431314504175e-08</v>
+        <v>0.1115948334469781</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43854694344216e-08</v>
+        <v>0.112621635939665</v>
       </c>
       <c r="P8" t="n">
-        <v>1.451783251448079e-08</v>
+        <v>0.1136578862116658</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.465141348909967e-08</v>
+        <v>0.1147036711935585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.478622356432722e-08</v>
+        <v>0.1157590786157832</v>
       </c>
       <c r="S8" t="n">
-        <v>1.492227404932113e-08</v>
+        <v>0.1168241970160028</v>
       </c>
       <c r="T8" t="n">
-        <v>1.505957635729653e-08</v>
+        <v>0.1178991157465296</v>
       </c>
       <c r="U8" t="n">
-        <v>1.519814200648338e-08</v>
+        <v>0.1189839249818212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1547206703910614</v>
+        <v>0.1359108159392777</v>
       </c>
       <c r="B9" t="n">
-        <v>1.253846715534884e-08</v>
+        <v>0.0968551871976584</v>
       </c>
       <c r="C9" t="n">
-        <v>1.265383566240165e-08</v>
+        <v>0.09774636777091908</v>
       </c>
       <c r="D9" t="n">
-        <v>1.277026569414122e-08</v>
+        <v>0.09864574824381482</v>
       </c>
       <c r="E9" t="n">
-        <v>1.288776701783151e-08</v>
+        <v>0.09955340406497641</v>
       </c>
       <c r="F9" t="n">
-        <v>1.300634949060669e-08</v>
+        <v>0.1004694113772499</v>
       </c>
       <c r="G9" t="n">
-        <v>1.312602306029803e-08</v>
+        <v>0.1013938470240844</v>
       </c>
       <c r="H9" t="n">
-        <v>1.324679776626848e-08</v>
+        <v>0.102326788555978</v>
       </c>
       <c r="I9" t="n">
-        <v>1.336868374025477e-08</v>
+        <v>0.1032683142369841</v>
       </c>
       <c r="J9" t="n">
-        <v>1.349169120721746e-08</v>
+        <v>0.1042185030512761</v>
       </c>
       <c r="K9" t="n">
-        <v>1.361583048619863e-08</v>
+        <v>0.1051774347097743</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37411119911876e-08</v>
+        <v>0.1061451896568321</v>
       </c>
       <c r="M9" t="n">
-        <v>1.386754623199449e-08</v>
+        <v>0.1071218490769848</v>
       </c>
       <c r="N9" t="n">
-        <v>1.399514381513195e-08</v>
+        <v>0.1081074949017597</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41239154447049e-08</v>
+        <v>0.1091022098165501</v>
       </c>
       <c r="P9" t="n">
-        <v>1.425387192330847e-08</v>
+        <v>0.1101060772675509</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.438502415293428e-08</v>
+        <v>0.1111191814687594</v>
       </c>
       <c r="R9" t="n">
-        <v>1.451738313588496e-08</v>
+        <v>0.1121416074090396</v>
       </c>
       <c r="S9" t="n">
-        <v>1.465095997569717e-08</v>
+        <v>0.1131734408592523</v>
       </c>
       <c r="T9" t="n">
-        <v>1.478576587807301e-08</v>
+        <v>0.1142147683794501</v>
       </c>
       <c r="U9" t="n">
-        <v>1.492181215182011e-08</v>
+        <v>0.1152656773261389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1685921787709494</v>
+        <v>0.1540322580645155</v>
       </c>
       <c r="B10" t="n">
-        <v>1.346724250018952e-08</v>
+        <v>0.1046660893910179</v>
       </c>
       <c r="C10" t="n">
-        <v>1.359115682257958e-08</v>
+        <v>0.105629139365348</v>
       </c>
       <c r="D10" t="n">
-        <v>1.371621130111467e-08</v>
+        <v>0.1066010505215418</v>
       </c>
       <c r="E10" t="n">
-        <v>1.384241642655979e-08</v>
+        <v>0.1075819043927971</v>
       </c>
       <c r="F10" t="n">
-        <v>1.396978278620721e-08</v>
+        <v>0.108571783262512</v>
       </c>
       <c r="G10" t="n">
-        <v>1.409832106476458e-08</v>
+        <v>0.1095707701711879</v>
       </c>
       <c r="H10" t="n">
-        <v>1.422804204525135e-08</v>
+        <v>0.1105789489233956</v>
       </c>
       <c r="I10" t="n">
-        <v>1.43589566099033e-08</v>
+        <v>0.1115964040948053</v>
       </c>
       <c r="J10" t="n">
-        <v>1.449107574108545e-08</v>
+        <v>0.1126232210392822</v>
       </c>
       <c r="K10" t="n">
-        <v>1.462441052221337e-08</v>
+        <v>0.1136594858960464</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4758972138683e-08</v>
+        <v>0.1147052855968992</v>
       </c>
       <c r="M10" t="n">
-        <v>1.489477187880893e-08</v>
+        <v>0.1157607078735157</v>
       </c>
       <c r="N10" t="n">
-        <v>1.503182113477138e-08</v>
+        <v>0.1168258412648048</v>
       </c>
       <c r="O10" t="n">
-        <v>1.517013140357196e-08</v>
+        <v>0.1179007751243364</v>
       </c>
       <c r="P10" t="n">
-        <v>1.530971428799801e-08</v>
+        <v>0.1189855996278372</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.545058149759611e-08</v>
+        <v>0.1200804057807561</v>
       </c>
       <c r="R10" t="n">
-        <v>1.559274484965425e-08</v>
+        <v>0.1211852854258976</v>
       </c>
       <c r="S10" t="n">
-        <v>1.573621627019329e-08</v>
+        <v>0.1223003312511275</v>
       </c>
       <c r="T10" t="n">
-        <v>1.588100779496733e-08</v>
+        <v>0.1234256367971477</v>
       </c>
       <c r="U10" t="n">
-        <v>1.602713157047347e-08</v>
+        <v>0.1245612964653436</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1813966480446922</v>
+        <v>0.1748719165085383</v>
       </c>
       <c r="B11" t="n">
-        <v>1.416382400881998e-08</v>
+        <v>0.1124769915843783</v>
       </c>
       <c r="C11" t="n">
-        <v>1.429414769271296e-08</v>
+        <v>0.1135119109597778</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44256705063447e-08</v>
+        <v>0.1145563527992697</v>
       </c>
       <c r="E11" t="n">
-        <v>1.455840348310595e-08</v>
+        <v>0.1156104047206186</v>
       </c>
       <c r="F11" t="n">
-        <v>1.469235775790754e-08</v>
+        <v>0.116674155147775</v>
       </c>
       <c r="G11" t="n">
-        <v>1.482754456811443e-08</v>
+        <v>0.1177476933182924</v>
       </c>
       <c r="H11" t="n">
-        <v>1.496397525448845e-08</v>
+        <v>0.1188311092908141</v>
       </c>
       <c r="I11" t="n">
-        <v>1.510166126213964e-08</v>
+        <v>0.1199244939526275</v>
       </c>
       <c r="J11" t="n">
-        <v>1.524061414148638e-08</v>
+        <v>0.1210279390272893</v>
       </c>
       <c r="K11" t="n">
-        <v>1.538084554922437e-08</v>
+        <v>0.1221415370823195</v>
       </c>
       <c r="L11" t="n">
-        <v>1.55223672493045e-08</v>
+        <v>0.1232653815369672</v>
       </c>
       <c r="M11" t="n">
-        <v>1.566519111391969e-08</v>
+        <v>0.1243995666700477</v>
       </c>
       <c r="N11" t="n">
-        <v>1.580932912450089e-08</v>
+        <v>0.1255441876278509</v>
       </c>
       <c r="O11" t="n">
-        <v>1.595479337272219e-08</v>
+        <v>0.1266993404321236</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61015960615151e-08</v>
+        <v>0.1278651219881246</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.624974950609241e-08</v>
+        <v>0.1290416300927538</v>
       </c>
       <c r="R11" t="n">
-        <v>1.639926613498115e-08</v>
+        <v>0.1302289634427566</v>
       </c>
       <c r="S11" t="n">
-        <v>1.655015849106531e-08</v>
+        <v>0.1314272216430037</v>
       </c>
       <c r="T11" t="n">
-        <v>1.670243923263802e-08</v>
+        <v>0.1326365052148463</v>
       </c>
       <c r="U11" t="n">
-        <v>1.685612113446344e-08</v>
+        <v>0.1338569156045494</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.194201117318435</v>
+        <v>0.1866508538899422</v>
       </c>
       <c r="B12" t="n">
-        <v>1.532479318987077e-08</v>
+        <v>0.1234122546550811</v>
       </c>
       <c r="C12" t="n">
-        <v>1.546579914293531e-08</v>
+        <v>0.1245477911919778</v>
       </c>
       <c r="D12" t="n">
-        <v>1.560810251506145e-08</v>
+        <v>0.1256937759880869</v>
       </c>
       <c r="E12" t="n">
-        <v>1.575171524401625e-08</v>
+        <v>0.126850305179567</v>
       </c>
       <c r="F12" t="n">
-        <v>1.589664937740814e-08</v>
+        <v>0.1280174757871413</v>
       </c>
       <c r="G12" t="n">
-        <v>1.604291707369756e-08</v>
+        <v>0.1291953857242368</v>
       </c>
       <c r="H12" t="n">
-        <v>1.619053060321699e-08</v>
+        <v>0.1303841338051981</v>
       </c>
       <c r="I12" t="n">
-        <v>1.633950234920024e-08</v>
+        <v>0.1315838197535767</v>
       </c>
       <c r="J12" t="n">
-        <v>1.64898448088213e-08</v>
+        <v>0.1327945442104973</v>
       </c>
       <c r="K12" t="n">
-        <v>1.664157059424273e-08</v>
+        <v>0.1340164087430998</v>
       </c>
       <c r="L12" t="n">
-        <v>1.679469243367369e-08</v>
+        <v>0.1352495158530606</v>
       </c>
       <c r="M12" t="n">
-        <v>1.694922317243767e-08</v>
+        <v>0.1364939689851905</v>
       </c>
       <c r="N12" t="n">
-        <v>1.710517577405012e-08</v>
+        <v>0.1377498725361134</v>
       </c>
       <c r="O12" t="n">
-        <v>1.726256332130595e-08</v>
+        <v>0.1390173318630238</v>
       </c>
       <c r="P12" t="n">
-        <v>1.742139901737697e-08</v>
+        <v>0.1402964532925248</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.758169618691963e-08</v>
+        <v>0.1415873441295485</v>
       </c>
       <c r="R12" t="n">
-        <v>1.774346827719269e-08</v>
+        <v>0.1428901126663572</v>
       </c>
       <c r="S12" t="n">
-        <v>1.790672885918539e-08</v>
+        <v>0.1442048681916283</v>
       </c>
       <c r="T12" t="n">
-        <v>1.807149162875586e-08</v>
+        <v>0.1455317209996222</v>
       </c>
       <c r="U12" t="n">
-        <v>1.823777040778009e-08</v>
+        <v>0.1468707823994353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2112737430167596</v>
+        <v>0.2002419354838698</v>
       </c>
       <c r="B13" t="n">
-        <v>1.671795620713179e-08</v>
+        <v>0.1327853372871127</v>
       </c>
       <c r="C13" t="n">
-        <v>1.68717808832022e-08</v>
+        <v>0.1340071171052927</v>
       </c>
       <c r="D13" t="n">
-        <v>1.702702092552162e-08</v>
+        <v>0.1352401387213594</v>
       </c>
       <c r="E13" t="n">
-        <v>1.718368935710868e-08</v>
+        <v>0.1364845055729519</v>
       </c>
       <c r="F13" t="n">
-        <v>1.734179932080891e-08</v>
+        <v>0.137740322049456</v>
       </c>
       <c r="G13" t="n">
-        <v>1.750136408039738e-08</v>
+        <v>0.1390076935007613</v>
       </c>
       <c r="H13" t="n">
-        <v>1.76623970216913e-08</v>
+        <v>0.1402867262460993</v>
       </c>
       <c r="I13" t="n">
-        <v>1.782491165367303e-08</v>
+        <v>0.1415775275829625</v>
       </c>
       <c r="J13" t="n">
-        <v>1.798892160962328e-08</v>
+        <v>0.1428802057961048</v>
       </c>
       <c r="K13" t="n">
-        <v>1.815444064826484e-08</v>
+        <v>0.1441948701666265</v>
       </c>
       <c r="L13" t="n">
-        <v>1.83214826549168e-08</v>
+        <v>0.1455216309811412</v>
       </c>
       <c r="M13" t="n">
-        <v>1.849006164265932e-08</v>
+        <v>0.1468605995410279</v>
       </c>
       <c r="N13" t="n">
-        <v>1.866019175350927e-08</v>
+        <v>0.1482118881717678</v>
       </c>
       <c r="O13" t="n">
-        <v>1.883188725960653e-08</v>
+        <v>0.1495756102323675</v>
       </c>
       <c r="P13" t="n">
-        <v>1.900516256441129e-08</v>
+        <v>0.1509518801248686</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.918003220391237e-08</v>
+        <v>0.1523408133039447</v>
       </c>
       <c r="R13" t="n">
-        <v>1.935651084784662e-08</v>
+        <v>0.153742526286587</v>
       </c>
       <c r="S13" t="n">
-        <v>1.953461330092957e-08</v>
+        <v>0.1551571366618787</v>
       </c>
       <c r="T13" t="n">
-        <v>1.971435450409735e-08</v>
+        <v>0.1565847631008595</v>
       </c>
       <c r="U13" t="n">
-        <v>1.989574953576014e-08</v>
+        <v>0.1580255253664812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2262122905027927</v>
+        <v>0.2147390891840601</v>
       </c>
       <c r="B14" t="n">
-        <v>1.880770073302326e-08</v>
+        <v>0.1468449612351605</v>
       </c>
       <c r="C14" t="n">
-        <v>1.898075349360248e-08</v>
+        <v>0.1481961059752655</v>
       </c>
       <c r="D14" t="n">
-        <v>1.915539854121183e-08</v>
+        <v>0.1495596828212687</v>
       </c>
       <c r="E14" t="n">
-        <v>1.933165052674727e-08</v>
+        <v>0.1509358061630298</v>
       </c>
       <c r="F14" t="n">
-        <v>1.950952423591003e-08</v>
+        <v>0.1523245914429284</v>
       </c>
       <c r="G14" t="n">
-        <v>1.968903459044705e-08</v>
+        <v>0.1537261551655484</v>
       </c>
       <c r="H14" t="n">
-        <v>1.987019664940272e-08</v>
+        <v>0.1551406149074517</v>
       </c>
       <c r="I14" t="n">
-        <v>2.005302561038216e-08</v>
+        <v>0.1565680893270415</v>
       </c>
       <c r="J14" t="n">
-        <v>2.023753681082619e-08</v>
+        <v>0.1580086981745165</v>
       </c>
       <c r="K14" t="n">
-        <v>2.042374572929795e-08</v>
+        <v>0.159462562301917</v>
       </c>
       <c r="L14" t="n">
-        <v>2.06116679867814e-08</v>
+        <v>0.1609298036732628</v>
       </c>
       <c r="M14" t="n">
-        <v>2.080131934799174e-08</v>
+        <v>0.1624105453747845</v>
       </c>
       <c r="N14" t="n">
-        <v>2.099271572269793e-08</v>
+        <v>0.1639049116252497</v>
       </c>
       <c r="O14" t="n">
-        <v>2.118587316705735e-08</v>
+        <v>0.1654130277863836</v>
       </c>
       <c r="P14" t="n">
-        <v>2.13808078849627e-08</v>
+        <v>0.1669350203733848</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.157753622940142e-08</v>
+        <v>0.1684710170655396</v>
       </c>
       <c r="R14" t="n">
-        <v>2.177607470382745e-08</v>
+        <v>0.1700211467169322</v>
       </c>
       <c r="S14" t="n">
-        <v>2.197643996354576e-08</v>
+        <v>0.1715855393672548</v>
       </c>
       <c r="T14" t="n">
-        <v>2.217864881710952e-08</v>
+        <v>0.1731643262527159</v>
       </c>
       <c r="U14" t="n">
-        <v>2.238271822773016e-08</v>
+        <v>0.1747576398170505</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2422178770949723</v>
+        <v>0.2274240986717265</v>
       </c>
       <c r="B15" t="n">
-        <v>2.112963909512496e-08</v>
+        <v>0.1671533069378949</v>
       </c>
       <c r="C15" t="n">
-        <v>2.132405639404729e-08</v>
+        <v>0.1686913121207803</v>
       </c>
       <c r="D15" t="n">
-        <v>2.152026255864545e-08</v>
+        <v>0.1702434687433584</v>
       </c>
       <c r="E15" t="n">
-        <v>2.171827404856798e-08</v>
+        <v>0.1718099070153631</v>
       </c>
       <c r="F15" t="n">
-        <v>2.191810747491134e-08</v>
+        <v>0.1733907583446094</v>
       </c>
       <c r="G15" t="n">
-        <v>2.211977960161342e-08</v>
+        <v>0.1749861553480173</v>
       </c>
       <c r="H15" t="n">
-        <v>2.232330734685991e-08</v>
+        <v>0.176596231862737</v>
       </c>
       <c r="I15" t="n">
-        <v>2.252870778450348e-08</v>
+        <v>0.1782211229573764</v>
       </c>
       <c r="J15" t="n">
-        <v>2.273599814549615e-08</v>
+        <v>0.179860964943332</v>
       </c>
       <c r="K15" t="n">
-        <v>2.29451958193348e-08</v>
+        <v>0.1815158953862241</v>
       </c>
       <c r="L15" t="n">
-        <v>2.315631835551991e-08</v>
+        <v>0.1831860531174368</v>
       </c>
       <c r="M15" t="n">
-        <v>2.336938346502783e-08</v>
+        <v>0.1848715782457647</v>
       </c>
       <c r="N15" t="n">
-        <v>2.358440902179651e-08</v>
+        <v>0.1865726121691666</v>
       </c>
       <c r="O15" t="n">
-        <v>2.380141306422499e-08</v>
+        <v>0.1882892975866275</v>
       </c>
       <c r="P15" t="n">
-        <v>2.402041379668656e-08</v>
+        <v>0.1900217785101289</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.424142959105599e-08</v>
+        <v>0.1917702002767306</v>
       </c>
       <c r="R15" t="n">
-        <v>2.446447898825066e-08</v>
+        <v>0.1935347095607626</v>
       </c>
       <c r="S15" t="n">
-        <v>2.468958069978605e-08</v>
+        <v>0.1953154543861298</v>
       </c>
       <c r="T15" t="n">
-        <v>2.491675360934533e-08</v>
+        <v>0.1971125841387292</v>
       </c>
       <c r="U15" t="n">
-        <v>2.514601677436359e-08</v>
+        <v>0.1989262495789824</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2528882681564248</v>
+        <v>0.2382969639468679</v>
       </c>
       <c r="B16" t="n">
-        <v>2.345157745722655e-08</v>
+        <v>0.1812129308859428</v>
       </c>
       <c r="C16" t="n">
-        <v>2.366735929449199e-08</v>
+        <v>0.1828803009907531</v>
       </c>
       <c r="D16" t="n">
-        <v>2.388512657607896e-08</v>
+        <v>0.1845630128432677</v>
       </c>
       <c r="E16" t="n">
-        <v>2.410489757038858e-08</v>
+        <v>0.186261207605441</v>
       </c>
       <c r="F16" t="n">
-        <v>2.432669071391252e-08</v>
+        <v>0.1879750277380818</v>
       </c>
       <c r="G16" t="n">
-        <v>2.455052461277967e-08</v>
+        <v>0.1897046170128044</v>
       </c>
       <c r="H16" t="n">
-        <v>2.477641804431698e-08</v>
+        <v>0.1914501205240893</v>
       </c>
       <c r="I16" t="n">
-        <v>2.500438995862468e-08</v>
+        <v>0.1932116847014554</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5234459480166e-08</v>
+        <v>0.1949894573217438</v>
       </c>
       <c r="K16" t="n">
-        <v>2.546664590937153e-08</v>
+        <v>0.1967835875215146</v>
       </c>
       <c r="L16" t="n">
-        <v>2.57009687242583e-08</v>
+        <v>0.1985942258095583</v>
       </c>
       <c r="M16" t="n">
-        <v>2.593744758206379e-08</v>
+        <v>0.2004215240795212</v>
       </c>
       <c r="N16" t="n">
-        <v>2.617610232089496e-08</v>
+        <v>0.2022656356226486</v>
       </c>
       <c r="O16" t="n">
-        <v>2.641695296139251e-08</v>
+        <v>0.2041267151406436</v>
       </c>
       <c r="P16" t="n">
-        <v>2.666001970841029e-08</v>
+        <v>0.206004918758645</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.690532295271042e-08</v>
+        <v>0.2079004040383254</v>
       </c>
       <c r="R16" t="n">
-        <v>2.715288327267374e-08</v>
+        <v>0.2098133299911078</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74027214360262e-08</v>
+        <v>0.2117438570915059</v>
       </c>
       <c r="T16" t="n">
-        <v>2.765485840158102e-08</v>
+        <v>0.2136921472905856</v>
       </c>
       <c r="U16" t="n">
-        <v>2.790931532099688e-08</v>
+        <v>0.2156583640295517</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.2688938547486029</v>
+        <v>0.2518880455407969</v>
       </c>
       <c r="B17" t="n">
-        <v>2.554132198311802e-08</v>
+        <v>0.1968347352726618</v>
       </c>
       <c r="C17" t="n">
-        <v>2.577633190489226e-08</v>
+        <v>0.198645844179611</v>
       </c>
       <c r="D17" t="n">
-        <v>2.601350419176916e-08</v>
+        <v>0.2004736173987217</v>
       </c>
       <c r="E17" t="n">
-        <v>2.625285874002716e-08</v>
+        <v>0.2023182082610823</v>
       </c>
       <c r="F17" t="n">
-        <v>2.649441562901363e-08</v>
+        <v>0.2041797715086059</v>
       </c>
       <c r="G17" t="n">
-        <v>2.673819512282934e-08</v>
+        <v>0.2060584633070115</v>
       </c>
       <c r="H17" t="n">
-        <v>2.698421767202839e-08</v>
+        <v>0.2079544412589244</v>
       </c>
       <c r="I17" t="n">
-        <v>2.723250391533381e-08</v>
+        <v>0.2098678644170979</v>
       </c>
       <c r="J17" t="n">
-        <v>2.748307468136891e-08</v>
+        <v>0.211798893297756</v>
       </c>
       <c r="K17" t="n">
-        <v>2.773595099040463e-08</v>
+        <v>0.2137476898940588</v>
       </c>
       <c r="L17" t="n">
-        <v>2.79911540561229e-08</v>
+        <v>0.2157144176896924</v>
       </c>
       <c r="M17" t="n">
-        <v>2.82487052873962e-08</v>
+        <v>0.2176992416725833</v>
       </c>
       <c r="N17" t="n">
-        <v>2.850862629008362e-08</v>
+        <v>0.2197023283487388</v>
       </c>
       <c r="O17" t="n">
-        <v>2.877093886884332e-08</v>
+        <v>0.2217238457562161</v>
       </c>
       <c r="P17" t="n">
-        <v>2.903566502896171e-08</v>
+        <v>0.2237639634792177</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.930282697819947e-08</v>
+        <v>0.2258228526623188</v>
       </c>
       <c r="R17" t="n">
-        <v>2.957244712865457e-08</v>
+        <v>0.2279006860248238</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98445480986424e-08</v>
+        <v>0.2299976378752562</v>
       </c>
       <c r="T17" t="n">
-        <v>3.011915271459318e-08</v>
+        <v>0.2321138841259807</v>
       </c>
       <c r="U17" t="n">
-        <v>3.03962840129669e-08</v>
+        <v>0.2342496023079611</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.2838324022346361</v>
+        <v>0.264573055028462</v>
       </c>
       <c r="B18" t="n">
-        <v>2.809545418142984e-08</v>
+        <v>0.2124565396593809</v>
       </c>
       <c r="C18" t="n">
-        <v>2.83539650953815e-08</v>
+        <v>0.2144113873684688</v>
       </c>
       <c r="D18" t="n">
-        <v>2.861485461094609e-08</v>
+        <v>0.2163842219541756</v>
       </c>
       <c r="E18" t="n">
-        <v>2.887814461402989e-08</v>
+        <v>0.2183752089167236</v>
       </c>
       <c r="F18" t="n">
-        <v>2.914385719191501e-08</v>
+        <v>0.2203845152791301</v>
       </c>
       <c r="G18" t="n">
-        <v>2.941201463511229e-08</v>
+        <v>0.2224123096012186</v>
       </c>
       <c r="H18" t="n">
-        <v>2.968263943923124e-08</v>
+        <v>0.2244587619937595</v>
       </c>
       <c r="I18" t="n">
-        <v>2.99557543068672e-08</v>
+        <v>0.2265240441327405</v>
       </c>
       <c r="J18" t="n">
-        <v>3.023138214950581e-08</v>
+        <v>0.2286083292737682</v>
       </c>
       <c r="K18" t="n">
-        <v>3.050954608944511e-08</v>
+        <v>0.230711792266603</v>
       </c>
       <c r="L18" t="n">
-        <v>3.07902694617352e-08</v>
+        <v>0.2328346095698266</v>
       </c>
       <c r="M18" t="n">
-        <v>3.107357581613583e-08</v>
+        <v>0.2349769592656452</v>
       </c>
       <c r="N18" t="n">
-        <v>3.135948891909199e-08</v>
+        <v>0.237139021074829</v>
       </c>
       <c r="O18" t="n">
-        <v>3.164803275572767e-08</v>
+        <v>0.2393209763717886</v>
       </c>
       <c r="P18" t="n">
-        <v>3.193923153185789e-08</v>
+        <v>0.2415230081997904</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.223310967601943e-08</v>
+        <v>0.2437453012863122</v>
       </c>
       <c r="R18" t="n">
-        <v>3.252969184152004e-08</v>
+        <v>0.2459880420585398</v>
       </c>
       <c r="S18" t="n">
-        <v>3.282900290850665e-08</v>
+        <v>0.2482514186590065</v>
       </c>
       <c r="T18" t="n">
-        <v>3.313106798605251e-08</v>
+        <v>0.2505356209613758</v>
       </c>
       <c r="U18" t="n">
-        <v>3.34359124142636e-08</v>
+        <v>0.2528408405863706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.2987709497206705</v>
+        <v>0.2790702087286522</v>
       </c>
       <c r="B19" t="n">
-        <v>3.041739254353153e-08</v>
+        <v>0.231202704923444</v>
       </c>
       <c r="C19" t="n">
-        <v>3.069726799582631e-08</v>
+        <v>0.2333300391950986</v>
       </c>
       <c r="D19" t="n">
-        <v>3.097971862837971e-08</v>
+        <v>0.2354769474207207</v>
       </c>
       <c r="E19" t="n">
-        <v>3.12647681358506e-08</v>
+        <v>0.2376436097034935</v>
       </c>
       <c r="F19" t="n">
-        <v>3.155244043091631e-08</v>
+        <v>0.2398302078037594</v>
       </c>
       <c r="G19" t="n">
-        <v>3.184275964627866e-08</v>
+        <v>0.2420369251542674</v>
       </c>
       <c r="H19" t="n">
-        <v>3.213575013668844e-08</v>
+        <v>0.244263946875562</v>
       </c>
       <c r="I19" t="n">
-        <v>3.243143648098852e-08</v>
+        <v>0.2465114597915119</v>
       </c>
       <c r="J19" t="n">
-        <v>3.272984348417577e-08</v>
+        <v>0.2487796524449832</v>
       </c>
       <c r="K19" t="n">
-        <v>3.303099617948196e-08</v>
+        <v>0.2510687151136564</v>
       </c>
       <c r="L19" t="n">
-        <v>3.333491983047371e-08</v>
+        <v>0.2533788398259879</v>
       </c>
       <c r="M19" t="n">
-        <v>3.364163993317192e-08</v>
+        <v>0.25571022037732</v>
       </c>
       <c r="N19" t="n">
-        <v>3.395118221819057e-08</v>
+        <v>0.2580630523461376</v>
       </c>
       <c r="O19" t="n">
-        <v>3.426357265289532e-08</v>
+        <v>0.2604375331104761</v>
       </c>
       <c r="P19" t="n">
-        <v>3.457883744358175e-08</v>
+        <v>0.2628338618644779</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4897003037674e-08</v>
+        <v>0.2652522396351047</v>
       </c>
       <c r="R19" t="n">
-        <v>3.521809612594325e-08</v>
+        <v>0.2676928692989994</v>
       </c>
       <c r="S19" t="n">
-        <v>3.554214364474694e-08</v>
+        <v>0.2701559555995073</v>
       </c>
       <c r="T19" t="n">
-        <v>3.586917277828833e-08</v>
+        <v>0.2726417051638504</v>
       </c>
       <c r="U19" t="n">
-        <v>3.619921096089702e-08</v>
+        <v>0.2751503265204623</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3105083798882682</v>
+        <v>0.2899430740037949</v>
       </c>
       <c r="B20" t="n">
-        <v>3.227494323321289e-08</v>
+        <v>0.2437001484328189</v>
       </c>
       <c r="C20" t="n">
-        <v>3.257191031618217e-08</v>
+        <v>0.2459424737461846</v>
       </c>
       <c r="D20" t="n">
-        <v>3.28716098423266e-08</v>
+        <v>0.2482054310650835</v>
       </c>
       <c r="E20" t="n">
-        <v>3.317406695330717e-08</v>
+        <v>0.2504892102280062</v>
       </c>
       <c r="F20" t="n">
-        <v>3.347930702211735e-08</v>
+        <v>0.2527940028201783</v>
       </c>
       <c r="G20" t="n">
-        <v>3.378735565521175e-08</v>
+        <v>0.2551200021896328</v>
       </c>
       <c r="H20" t="n">
-        <v>3.409823869465418e-08</v>
+        <v>0.2574674034634297</v>
       </c>
       <c r="I20" t="n">
-        <v>3.441198222028557e-08</v>
+        <v>0.2598364035640255</v>
       </c>
       <c r="J20" t="n">
-        <v>3.472861255191175e-08</v>
+        <v>0.2622272012257926</v>
       </c>
       <c r="K20" t="n">
-        <v>3.504815625151144e-08</v>
+        <v>0.2646399970116914</v>
       </c>
       <c r="L20" t="n">
-        <v>3.537064012546452e-08</v>
+        <v>0.2670749933300949</v>
       </c>
       <c r="M20" t="n">
-        <v>3.569609122680078e-08</v>
+        <v>0.2695323944517692</v>
       </c>
       <c r="N20" t="n">
-        <v>3.602453685746943e-08</v>
+        <v>0.2720124065270094</v>
       </c>
       <c r="O20" t="n">
-        <v>3.635600457062943e-08</v>
+        <v>0.2745152376029337</v>
       </c>
       <c r="P20" t="n">
-        <v>3.669052217296084e-08</v>
+        <v>0.2770410976409357</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.702811772699765e-08</v>
+        <v>0.279590198534299</v>
       </c>
       <c r="R20" t="n">
-        <v>3.736881955348182e-08</v>
+        <v>0.2821627541259717</v>
       </c>
       <c r="S20" t="n">
-        <v>3.771265623373918e-08</v>
+        <v>0.2847589802265071</v>
       </c>
       <c r="T20" t="n">
-        <v>3.805965661207698e-08</v>
+        <v>0.287379094632166</v>
       </c>
       <c r="U20" t="n">
-        <v>3.840984979820377e-08</v>
+        <v>0.2900233171431894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3243798882681561</v>
+        <v>0.3008159392789362</v>
       </c>
       <c r="B21" t="n">
-        <v>3.413249392289414e-08</v>
+        <v>0.2577597723808667</v>
       </c>
       <c r="C21" t="n">
-        <v>3.44465526365379e-08</v>
+        <v>0.2601314626161573</v>
       </c>
       <c r="D21" t="n">
-        <v>3.476350105627339e-08</v>
+        <v>0.2625249751649927</v>
       </c>
       <c r="E21" t="n">
-        <v>3.508336577076363e-08</v>
+        <v>0.2649405108180841</v>
       </c>
       <c r="F21" t="n">
-        <v>3.540617361331828e-08</v>
+        <v>0.2673782722136508</v>
       </c>
       <c r="G21" t="n">
-        <v>3.573195166414473e-08</v>
+        <v>0.2698384638544199</v>
       </c>
       <c r="H21" t="n">
-        <v>3.606072725261982e-08</v>
+        <v>0.2723212921247821</v>
       </c>
       <c r="I21" t="n">
-        <v>3.639252795958251e-08</v>
+        <v>0.2748269653081046</v>
       </c>
       <c r="J21" t="n">
-        <v>3.672738161964761e-08</v>
+        <v>0.2773556936042044</v>
       </c>
       <c r="K21" t="n">
-        <v>3.70653163235408e-08</v>
+        <v>0.2799076891469819</v>
       </c>
       <c r="L21" t="n">
-        <v>3.740636042045521e-08</v>
+        <v>0.2824831660222164</v>
       </c>
       <c r="M21" t="n">
-        <v>3.775054252042953e-08</v>
+        <v>0.2850823402855258</v>
       </c>
       <c r="N21" t="n">
-        <v>3.809789149674817e-08</v>
+        <v>0.2877054299804914</v>
       </c>
       <c r="O21" t="n">
-        <v>3.844843648836342e-08</v>
+        <v>0.2903526551569497</v>
       </c>
       <c r="P21" t="n">
-        <v>3.88022069023398e-08</v>
+        <v>0.2930242378894519</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.915923241632117e-08</v>
+        <v>0.2957204022958938</v>
       </c>
       <c r="R21" t="n">
-        <v>3.951954298102026e-08</v>
+        <v>0.298441374556317</v>
       </c>
       <c r="S21" t="n">
-        <v>3.988316882273128e-08</v>
+        <v>0.3011873829318832</v>
       </c>
       <c r="T21" t="n">
-        <v>4.025014044586551e-08</v>
+        <v>0.3039586577840225</v>
       </c>
       <c r="U21" t="n">
-        <v>4.062048863551038e-08</v>
+        <v>0.3067554315937587</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.3403854748603342</v>
+        <v>0.3144070208728652</v>
       </c>
       <c r="B22" t="n">
-        <v>3.552565694015516e-08</v>
+        <v>0.2718193963289137</v>
       </c>
       <c r="C22" t="n">
-        <v>3.585253437680479e-08</v>
+        <v>0.2743204514861293</v>
       </c>
       <c r="D22" t="n">
-        <v>3.618241946673357e-08</v>
+        <v>0.2768445192649011</v>
       </c>
       <c r="E22" t="n">
-        <v>3.651533988385606e-08</v>
+        <v>0.2793918114081611</v>
       </c>
       <c r="F22" t="n">
-        <v>3.685132355671907e-08</v>
+        <v>0.2819625416071223</v>
       </c>
       <c r="G22" t="n">
-        <v>3.719039867084455e-08</v>
+        <v>0.2845569255192061</v>
       </c>
       <c r="H22" t="n">
-        <v>3.753259367109414e-08</v>
+        <v>0.2871751807861335</v>
       </c>
       <c r="I22" t="n">
-        <v>3.787793726405531e-08</v>
+        <v>0.2898175270521826</v>
       </c>
       <c r="J22" t="n">
-        <v>3.822645842044959e-08</v>
+        <v>0.2924841859826152</v>
       </c>
       <c r="K22" t="n">
-        <v>3.857818637756291e-08</v>
+        <v>0.2951753812822714</v>
       </c>
       <c r="L22" t="n">
-        <v>3.893315064169832e-08</v>
+        <v>0.2978913387143369</v>
       </c>
       <c r="M22" t="n">
-        <v>3.929138099065119e-08</v>
+        <v>0.3006322861192814</v>
       </c>
       <c r="N22" t="n">
-        <v>3.965290747620732e-08</v>
+        <v>0.3033984534339724</v>
       </c>
       <c r="O22" t="n">
-        <v>4.001776042666401e-08</v>
+        <v>0.3061900727109649</v>
       </c>
       <c r="P22" t="n">
-        <v>4.038597044937412e-08</v>
+        <v>0.3090073781379671</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.075756843331393e-08</v>
+        <v>0.3118506060574877</v>
       </c>
       <c r="R22" t="n">
-        <v>4.113258555167419e-08</v>
+        <v>0.3147199949866611</v>
       </c>
       <c r="S22" t="n">
-        <v>4.151105326447545e-08</v>
+        <v>0.3176157856372583</v>
       </c>
       <c r="T22" t="n">
-        <v>4.1893003321207e-08</v>
+        <v>0.3205382209358779</v>
       </c>
       <c r="U22" t="n">
-        <v>4.227846776349043e-08</v>
+        <v>0.323487546044327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.3563910614525138</v>
+        <v>0.3279981024667929</v>
       </c>
       <c r="B23" t="n">
-        <v>3.71510137936263e-08</v>
+        <v>0.2827546593996174</v>
       </c>
       <c r="C23" t="n">
-        <v>3.74928464071161e-08</v>
+        <v>0.2853563317183301</v>
       </c>
       <c r="D23" t="n">
-        <v>3.783782427893704e-08</v>
+        <v>0.2879819424537192</v>
       </c>
       <c r="E23" t="n">
-        <v>3.81859763491305e-08</v>
+        <v>0.2906317118671103</v>
       </c>
       <c r="F23" t="n">
-        <v>3.853733182401991e-08</v>
+        <v>0.2933058622464895</v>
       </c>
       <c r="G23" t="n">
-        <v>3.889192017866095e-08</v>
+        <v>0.2960046179251514</v>
       </c>
       <c r="H23" t="n">
-        <v>3.924977115931411e-08</v>
+        <v>0.2987282053005184</v>
       </c>
       <c r="I23" t="n">
-        <v>3.961091478594018e-08</v>
+        <v>0.3014768528531328</v>
       </c>
       <c r="J23" t="n">
-        <v>3.99753813547185e-08</v>
+        <v>0.3042507911658242</v>
       </c>
       <c r="K23" t="n">
-        <v>4.034320144058864e-08</v>
+        <v>0.3070502529430528</v>
       </c>
       <c r="L23" t="n">
-        <v>4.071440589981521e-08</v>
+        <v>0.3098754730304312</v>
       </c>
       <c r="M23" t="n">
-        <v>4.108902587257639e-08</v>
+        <v>0.3127266884344252</v>
       </c>
       <c r="N23" t="n">
-        <v>4.146709278557627e-08</v>
+        <v>0.3156041383422359</v>
       </c>
       <c r="O23" t="n">
-        <v>4.184863835468129e-08</v>
+        <v>0.3185080641418661</v>
       </c>
       <c r="P23" t="n">
-        <v>4.223369458758075e-08</v>
+        <v>0.3214387094423683</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.262229378647205e-08</v>
+        <v>0.3243963200942834</v>
       </c>
       <c r="R23" t="n">
-        <v>4.301446855077038e-08</v>
+        <v>0.3273811442102628</v>
       </c>
       <c r="S23" t="n">
-        <v>4.341025177984359e-08</v>
+        <v>0.3303934321858839</v>
       </c>
       <c r="T23" t="n">
-        <v>4.3809676675772e-08</v>
+        <v>0.3334334367206548</v>
       </c>
       <c r="U23" t="n">
-        <v>4.421277674613377e-08</v>
+        <v>0.3365014128392141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.3734636871508371</v>
+        <v>0.3443074003795055</v>
       </c>
       <c r="B24" t="n">
-        <v>3.831198297467709e-08</v>
+        <v>0.2983764637863364</v>
       </c>
       <c r="C24" t="n">
-        <v>3.866449785733845e-08</v>
+        <v>0.3011218749071879</v>
       </c>
       <c r="D24" t="n">
-        <v>3.90202562876538e-08</v>
+        <v>0.3038925470091732</v>
       </c>
       <c r="E24" t="n">
-        <v>3.93792881100408e-08</v>
+        <v>0.3066887125227516</v>
       </c>
       <c r="F24" t="n">
-        <v>3.974162344352051e-08</v>
+        <v>0.3095106060170137</v>
       </c>
       <c r="G24" t="n">
-        <v>4.010729268424407e-08</v>
+        <v>0.3123584642193585</v>
       </c>
       <c r="H24" t="n">
-        <v>4.047632650804265e-08</v>
+        <v>0.3152325260353535</v>
       </c>
       <c r="I24" t="n">
-        <v>4.084875587300077e-08</v>
+        <v>0.3181330325687753</v>
       </c>
       <c r="J24" t="n">
-        <v>4.122461202205342e-08</v>
+        <v>0.3210602271418364</v>
       </c>
       <c r="K24" t="n">
-        <v>4.160392648560702e-08</v>
+        <v>0.324014355315597</v>
       </c>
       <c r="L24" t="n">
-        <v>4.198673108418441e-08</v>
+        <v>0.3269956649105654</v>
       </c>
       <c r="M24" t="n">
-        <v>4.237305793109437e-08</v>
+        <v>0.3300044060274872</v>
       </c>
       <c r="N24" t="n">
-        <v>4.27629394351255e-08</v>
+        <v>0.3330408310683262</v>
       </c>
       <c r="O24" t="n">
-        <v>4.315640830326506e-08</v>
+        <v>0.3361051947574386</v>
       </c>
       <c r="P24" t="n">
-        <v>4.355349754344262e-08</v>
+        <v>0.339197754162941</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.395424046729928e-08</v>
+        <v>0.3423187687182768</v>
       </c>
       <c r="R24" t="n">
-        <v>4.435867069298192e-08</v>
+        <v>0.3454685002439788</v>
       </c>
       <c r="S24" t="n">
-        <v>4.476682214796367e-08</v>
+        <v>0.3486472129696342</v>
       </c>
       <c r="T24" t="n">
-        <v>4.517872907188984e-08</v>
+        <v>0.35185517355605</v>
       </c>
       <c r="U24" t="n">
-        <v>4.559442601945041e-08</v>
+        <v>0.3550926511176234</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.3894692737430166</v>
+        <v>0.3606166982922195</v>
       </c>
       <c r="B25" t="n">
-        <v>3.877637064709743e-08</v>
+        <v>0.306187365979696</v>
       </c>
       <c r="C25" t="n">
-        <v>3.913315843742742e-08</v>
+        <v>0.3090046465016169</v>
       </c>
       <c r="D25" t="n">
-        <v>3.949322909114052e-08</v>
+        <v>0.3118478492869002</v>
       </c>
       <c r="E25" t="n">
-        <v>3.985661281440494e-08</v>
+        <v>0.3147172128505723</v>
       </c>
       <c r="F25" t="n">
-        <v>4.022334009132076e-08</v>
+        <v>0.3176129779022758</v>
       </c>
       <c r="G25" t="n">
-        <v>4.059344168647734e-08</v>
+        <v>0.3205353873664621</v>
       </c>
       <c r="H25" t="n">
-        <v>4.096694864753408e-08</v>
+        <v>0.3234846864027711</v>
       </c>
       <c r="I25" t="n">
-        <v>4.134389230782504e-08</v>
+        <v>0.3264611224265966</v>
       </c>
       <c r="J25" t="n">
-        <v>4.172430428898742e-08</v>
+        <v>0.3294649451298425</v>
       </c>
       <c r="K25" t="n">
-        <v>4.210821650361438e-08</v>
+        <v>0.3324964065018691</v>
       </c>
       <c r="L25" t="n">
-        <v>4.249566115793211e-08</v>
+        <v>0.3355557608506324</v>
       </c>
       <c r="M25" t="n">
-        <v>4.288667075450158e-08</v>
+        <v>0.3386432648240181</v>
       </c>
       <c r="N25" t="n">
-        <v>4.328127809494521e-08</v>
+        <v>0.3417591774313713</v>
       </c>
       <c r="O25" t="n">
-        <v>4.367951628269858e-08</v>
+        <v>0.3449037600652249</v>
       </c>
       <c r="P25" t="n">
-        <v>4.408141872578739e-08</v>
+        <v>0.3480772765232273</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.448701913963019e-08</v>
+        <v>0.3512799930302735</v>
       </c>
       <c r="R25" t="n">
-        <v>4.489635154986656e-08</v>
+        <v>0.3545121782608368</v>
       </c>
       <c r="S25" t="n">
-        <v>4.530945029521172e-08</v>
+        <v>0.3577741033615094</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5726350030337e-08</v>
+        <v>0.3610660419737476</v>
       </c>
       <c r="U25" t="n">
-        <v>4.61470857287771e-08</v>
+        <v>0.3643882702568282</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.4086759776536315</v>
+        <v>0.3778320683111948</v>
       </c>
       <c r="B26" t="n">
-        <v>3.877637064709743e-08</v>
+        <v>0.3108739072957122</v>
       </c>
       <c r="C26" t="n">
-        <v>3.913315843742742e-08</v>
+        <v>0.3137343094582748</v>
       </c>
       <c r="D26" t="n">
-        <v>3.949322909114052e-08</v>
+        <v>0.3166210306535369</v>
       </c>
       <c r="E26" t="n">
-        <v>3.985661281440494e-08</v>
+        <v>0.3195343130472653</v>
       </c>
       <c r="F26" t="n">
-        <v>4.022334009132076e-08</v>
+        <v>0.3224744010334335</v>
       </c>
       <c r="G26" t="n">
-        <v>4.059344168647734e-08</v>
+        <v>0.3254415412547248</v>
       </c>
       <c r="H26" t="n">
-        <v>4.096694864753408e-08</v>
+        <v>0.3284359826232222</v>
       </c>
       <c r="I26" t="n">
-        <v>4.134389230782504e-08</v>
+        <v>0.3314579763412899</v>
       </c>
       <c r="J26" t="n">
-        <v>4.172430428898742e-08</v>
+        <v>0.3345077759226467</v>
       </c>
       <c r="K26" t="n">
-        <v>4.210821650361438e-08</v>
+        <v>0.3375856372136329</v>
       </c>
       <c r="L26" t="n">
-        <v>4.249566115793211e-08</v>
+        <v>0.3406918184146733</v>
       </c>
       <c r="M26" t="n">
-        <v>4.288667075450158e-08</v>
+        <v>0.3438265801019373</v>
       </c>
       <c r="N26" t="n">
-        <v>4.328127809494521e-08</v>
+        <v>0.3469901852491989</v>
       </c>
       <c r="O26" t="n">
-        <v>4.367951628269858e-08</v>
+        <v>0.3501828992498972</v>
       </c>
       <c r="P26" t="n">
-        <v>4.408141872578739e-08</v>
+        <v>0.3534049899393997</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.448701913963019e-08</v>
+        <v>0.3566567276174722</v>
       </c>
       <c r="R26" t="n">
-        <v>4.489635154986656e-08</v>
+        <v>0.3599383850709522</v>
       </c>
       <c r="S26" t="n">
-        <v>4.530945029521172e-08</v>
+        <v>0.3632502375966352</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5726350030337e-08</v>
+        <v>0.3665925630243667</v>
       </c>
       <c r="U26" t="n">
-        <v>4.61470857287771e-08</v>
+        <v>0.3699656417403516</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.4257486033519548</v>
+        <v>0.3977656546489564</v>
       </c>
       <c r="B27" t="n">
-        <v>3.831198297467709e-08</v>
+        <v>0.3108739072957122</v>
       </c>
       <c r="C27" t="n">
-        <v>3.866449785733845e-08</v>
+        <v>0.3137343094582748</v>
       </c>
       <c r="D27" t="n">
-        <v>3.90202562876538e-08</v>
+        <v>0.3166210306535369</v>
       </c>
       <c r="E27" t="n">
-        <v>3.93792881100408e-08</v>
+        <v>0.3195343130472653</v>
       </c>
       <c r="F27" t="n">
-        <v>3.974162344352051e-08</v>
+        <v>0.3224744010334335</v>
       </c>
       <c r="G27" t="n">
-        <v>4.010729268424407e-08</v>
+        <v>0.3254415412547248</v>
       </c>
       <c r="H27" t="n">
-        <v>4.047632650804265e-08</v>
+        <v>0.3284359826232222</v>
       </c>
       <c r="I27" t="n">
-        <v>4.084875587300077e-08</v>
+        <v>0.3314579763412899</v>
       </c>
       <c r="J27" t="n">
-        <v>4.122461202205342e-08</v>
+        <v>0.3345077759226467</v>
       </c>
       <c r="K27" t="n">
-        <v>4.160392648560702e-08</v>
+        <v>0.3375856372136329</v>
       </c>
       <c r="L27" t="n">
-        <v>4.198673108418441e-08</v>
+        <v>0.3406918184146733</v>
       </c>
       <c r="M27" t="n">
-        <v>4.237305793109437e-08</v>
+        <v>0.3438265801019373</v>
       </c>
       <c r="N27" t="n">
-        <v>4.27629394351255e-08</v>
+        <v>0.3469901852491989</v>
       </c>
       <c r="O27" t="n">
-        <v>4.315640830326506e-08</v>
+        <v>0.3501828992498972</v>
       </c>
       <c r="P27" t="n">
-        <v>4.355349754344262e-08</v>
+        <v>0.3534049899393997</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.395424046729928e-08</v>
+        <v>0.3566567276174722</v>
       </c>
       <c r="R27" t="n">
-        <v>4.435867069298192e-08</v>
+        <v>0.3599383850709522</v>
       </c>
       <c r="S27" t="n">
-        <v>4.476682214796367e-08</v>
+        <v>0.3632502375966352</v>
       </c>
       <c r="T27" t="n">
-        <v>4.517872907188984e-08</v>
+        <v>0.3665925630243667</v>
       </c>
       <c r="U27" t="n">
-        <v>4.559442601945041e-08</v>
+        <v>0.3699656417403516</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.4438882681564246</v>
+        <v>0.4149810246679315</v>
       </c>
       <c r="B28" t="n">
-        <v>3.738320762983653e-08</v>
+        <v>0.3093117268570402</v>
       </c>
       <c r="C28" t="n">
-        <v>3.772717669716064e-08</v>
+        <v>0.3121577551393889</v>
       </c>
       <c r="D28" t="n">
-        <v>3.807431068068047e-08</v>
+        <v>0.3150299701979913</v>
       </c>
       <c r="E28" t="n">
-        <v>3.842463870131263e-08</v>
+        <v>0.3179286129817009</v>
       </c>
       <c r="F28" t="n">
-        <v>3.877819014792011e-08</v>
+        <v>0.320853926656381</v>
       </c>
       <c r="G28" t="n">
-        <v>3.913499467977765e-08</v>
+        <v>0.3238061566253039</v>
       </c>
       <c r="H28" t="n">
-        <v>3.949508222905989e-08</v>
+        <v>0.3267855505497385</v>
       </c>
       <c r="I28" t="n">
-        <v>3.985848300335236e-08</v>
+        <v>0.3297923583697255</v>
       </c>
       <c r="J28" t="n">
-        <v>4.022522748818557e-08</v>
+        <v>0.3328268323250453</v>
       </c>
       <c r="K28" t="n">
-        <v>4.059534644959239e-08</v>
+        <v>0.3358892269763784</v>
       </c>
       <c r="L28" t="n">
-        <v>4.096887093668912e-08</v>
+        <v>0.3389797992266597</v>
       </c>
       <c r="M28" t="n">
-        <v>4.134583228428006e-08</v>
+        <v>0.342098808342631</v>
       </c>
       <c r="N28" t="n">
-        <v>4.172626211548619e-08</v>
+        <v>0.3452465159765897</v>
       </c>
       <c r="O28" t="n">
-        <v>4.211019234439812e-08</v>
+        <v>0.3484231861883398</v>
       </c>
       <c r="P28" t="n">
-        <v>4.249765517875321e-08</v>
+        <v>0.3516290854673423</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.288868312263758e-08</v>
+        <v>0.3548644827550727</v>
       </c>
       <c r="R28" t="n">
-        <v>4.328330897921277e-08</v>
+        <v>0.3581296494675804</v>
       </c>
       <c r="S28" t="n">
-        <v>4.368156585346768e-08</v>
+        <v>0.3614248595182599</v>
       </c>
       <c r="T28" t="n">
-        <v>4.408348715499565e-08</v>
+        <v>0.364750389340827</v>
       </c>
       <c r="U28" t="n">
-        <v>4.448910660079718e-08</v>
+        <v>0.3681065179125105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.4588268156424576</v>
+        <v>0.4403510436432631</v>
       </c>
       <c r="B29" t="n">
-        <v>3.691881995741618e-08</v>
+        <v>0.2999386442250085</v>
       </c>
       <c r="C29" t="n">
-        <v>3.725851611707167e-08</v>
+        <v>0.3026984292260739</v>
       </c>
       <c r="D29" t="n">
-        <v>3.760133787719374e-08</v>
+        <v>0.3054836074647188</v>
       </c>
       <c r="E29" t="n">
-        <v>3.794731399694849e-08</v>
+        <v>0.3082944125883159</v>
       </c>
       <c r="F29" t="n">
-        <v>3.829647350011985e-08</v>
+        <v>0.3111310803940663</v>
       </c>
       <c r="G29" t="n">
-        <v>3.864884567754437e-08</v>
+        <v>0.3139938488487795</v>
       </c>
       <c r="H29" t="n">
-        <v>3.900446008956845e-08</v>
+        <v>0.3168829581088372</v>
       </c>
       <c r="I29" t="n">
-        <v>3.93633465685281e-08</v>
+        <v>0.3197986505403397</v>
       </c>
       <c r="J29" t="n">
-        <v>3.972553522125157e-08</v>
+        <v>0.3227411707394378</v>
       </c>
       <c r="K29" t="n">
-        <v>4.009105643158502e-08</v>
+        <v>0.3257107655528515</v>
       </c>
       <c r="L29" t="n">
-        <v>4.045994086294142e-08</v>
+        <v>0.328707684098579</v>
       </c>
       <c r="M29" t="n">
-        <v>4.083221946087284e-08</v>
+        <v>0.3317321777867935</v>
       </c>
       <c r="N29" t="n">
-        <v>4.120792345566646e-08</v>
+        <v>0.3347845003409353</v>
       </c>
       <c r="O29" t="n">
-        <v>4.158708436496459e-08</v>
+        <v>0.337864907818996</v>
       </c>
       <c r="P29" t="n">
-        <v>4.196973399640843e-08</v>
+        <v>0.3409736586349985</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.235590445030666e-08</v>
+        <v>0.3441110135806763</v>
       </c>
       <c r="R29" t="n">
-        <v>4.274562812232812e-08</v>
+        <v>0.3472772358473505</v>
       </c>
       <c r="S29" t="n">
-        <v>4.313893770621963e-08</v>
+        <v>0.3504725910480094</v>
       </c>
       <c r="T29" t="n">
-        <v>4.353586619654849e-08</v>
+        <v>0.3536973472395897</v>
       </c>
       <c r="U29" t="n">
-        <v>4.393644689147049e-08</v>
+        <v>0.3569517749454647</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.4791005586592177</v>
+        <v>0.4693453510436422</v>
       </c>
       <c r="B30" t="n">
-        <v>3.552565694015516e-08</v>
+        <v>0.2827546593996174</v>
       </c>
       <c r="C30" t="n">
-        <v>3.585253437680479e-08</v>
+        <v>0.2853563317183301</v>
       </c>
       <c r="D30" t="n">
-        <v>3.618241946673357e-08</v>
+        <v>0.2879819424537192</v>
       </c>
       <c r="E30" t="n">
-        <v>3.651533988385606e-08</v>
+        <v>0.2906317118671103</v>
       </c>
       <c r="F30" t="n">
-        <v>3.685132355671907e-08</v>
+        <v>0.2933058622464895</v>
       </c>
       <c r="G30" t="n">
-        <v>3.719039867084455e-08</v>
+        <v>0.2960046179251514</v>
       </c>
       <c r="H30" t="n">
-        <v>3.753259367109414e-08</v>
+        <v>0.2987282053005184</v>
       </c>
       <c r="I30" t="n">
-        <v>3.787793726405531e-08</v>
+        <v>0.3014768528531328</v>
       </c>
       <c r="J30" t="n">
-        <v>3.822645842044959e-08</v>
+        <v>0.3042507911658242</v>
       </c>
       <c r="K30" t="n">
-        <v>3.857818637756291e-08</v>
+        <v>0.3070502529430528</v>
       </c>
       <c r="L30" t="n">
-        <v>3.893315064169832e-08</v>
+        <v>0.3098754730304312</v>
       </c>
       <c r="M30" t="n">
-        <v>3.929138099065119e-08</v>
+        <v>0.3127266884344252</v>
       </c>
       <c r="N30" t="n">
-        <v>3.965290747620732e-08</v>
+        <v>0.3156041383422359</v>
       </c>
       <c r="O30" t="n">
-        <v>4.001776042666401e-08</v>
+        <v>0.3185080641418661</v>
       </c>
       <c r="P30" t="n">
-        <v>4.038597044937412e-08</v>
+        <v>0.3214387094423683</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.075756843331393e-08</v>
+        <v>0.3243963200942834</v>
       </c>
       <c r="R30" t="n">
-        <v>4.113258555167419e-08</v>
+        <v>0.3273811442102628</v>
       </c>
       <c r="S30" t="n">
-        <v>4.151105326447545e-08</v>
+        <v>0.3303934321858839</v>
       </c>
       <c r="T30" t="n">
-        <v>4.1893003321207e-08</v>
+        <v>0.3334334367206548</v>
       </c>
       <c r="U30" t="n">
-        <v>4.227846776349043e-08</v>
+        <v>0.3365014128392141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.4951061452513972</v>
+        <v>0.4974335863377601</v>
       </c>
       <c r="B31" t="n">
-        <v>3.413249392289414e-08</v>
+        <v>0.2671328550128984</v>
       </c>
       <c r="C31" t="n">
-        <v>3.44465526365379e-08</v>
+        <v>0.2695907885294722</v>
       </c>
       <c r="D31" t="n">
-        <v>3.476350105627339e-08</v>
+        <v>0.2720713378982653</v>
       </c>
       <c r="E31" t="n">
-        <v>3.508336577076363e-08</v>
+        <v>0.274574711211469</v>
       </c>
       <c r="F31" t="n">
-        <v>3.540617361331828e-08</v>
+        <v>0.2771011184759654</v>
       </c>
       <c r="G31" t="n">
-        <v>3.573195166414473e-08</v>
+        <v>0.2796507716309444</v>
       </c>
       <c r="H31" t="n">
-        <v>3.606072725261982e-08</v>
+        <v>0.2822238845656833</v>
       </c>
       <c r="I31" t="n">
-        <v>3.639252795958251e-08</v>
+        <v>0.2848206731374903</v>
       </c>
       <c r="J31" t="n">
-        <v>3.672738161964761e-08</v>
+        <v>0.2874413551898119</v>
       </c>
       <c r="K31" t="n">
-        <v>3.70653163235408e-08</v>
+        <v>0.2900861505705086</v>
       </c>
       <c r="L31" t="n">
-        <v>3.740636042045521e-08</v>
+        <v>0.292755281150297</v>
       </c>
       <c r="M31" t="n">
-        <v>3.775054252042953e-08</v>
+        <v>0.2954489708413632</v>
       </c>
       <c r="N31" t="n">
-        <v>3.809789149674817e-08</v>
+        <v>0.2981674456161457</v>
       </c>
       <c r="O31" t="n">
-        <v>3.844843648836342e-08</v>
+        <v>0.3009109335262935</v>
       </c>
       <c r="P31" t="n">
-        <v>3.88022069023398e-08</v>
+        <v>0.3036796647217957</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.915923241632117e-08</v>
+        <v>0.30647387147029</v>
       </c>
       <c r="R31" t="n">
-        <v>3.951954298102026e-08</v>
+        <v>0.3092937881765467</v>
       </c>
       <c r="S31" t="n">
-        <v>3.988316882273128e-08</v>
+        <v>0.3121396514021336</v>
       </c>
       <c r="T31" t="n">
-        <v>4.025014044586551e-08</v>
+        <v>0.3150116998852598</v>
       </c>
       <c r="U31" t="n">
-        <v>4.062048863551038e-08</v>
+        <v>0.3179101745608046</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.5153798882681558</v>
+        <v>0.5318643263757105</v>
       </c>
       <c r="B32" t="n">
-        <v>3.273933090563312e-08</v>
+        <v>0.245262328871491</v>
       </c>
       <c r="C32" t="n">
-        <v>3.304057089627102e-08</v>
+        <v>0.2475190280650705</v>
       </c>
       <c r="D32" t="n">
-        <v>3.334458264581322e-08</v>
+        <v>0.2497964915206291</v>
       </c>
       <c r="E32" t="n">
-        <v>3.36513916576712e-08</v>
+        <v>0.2520949102935706</v>
       </c>
       <c r="F32" t="n">
-        <v>3.39610236699175e-08</v>
+        <v>0.2544144771972309</v>
       </c>
       <c r="G32" t="n">
-        <v>3.42735046574449e-08</v>
+        <v>0.2567553868190537</v>
       </c>
       <c r="H32" t="n">
-        <v>3.458886083414551e-08</v>
+        <v>0.2591178355369134</v>
       </c>
       <c r="I32" t="n">
-        <v>3.490711865510972e-08</v>
+        <v>0.26150202153559</v>
       </c>
       <c r="J32" t="n">
-        <v>3.522830481884563e-08</v>
+        <v>0.2639081448233941</v>
       </c>
       <c r="K32" t="n">
-        <v>3.555244626951869e-08</v>
+        <v>0.266336407248946</v>
       </c>
       <c r="L32" t="n">
-        <v>3.58795701992121e-08</v>
+        <v>0.2687870125181085</v>
       </c>
       <c r="M32" t="n">
-        <v>3.620970405020788e-08</v>
+        <v>0.2712601662110756</v>
       </c>
       <c r="N32" t="n">
-        <v>3.654287551728903e-08</v>
+        <v>0.2737560757996186</v>
       </c>
       <c r="O32" t="n">
-        <v>3.687911255006284e-08</v>
+        <v>0.2762749506644912</v>
       </c>
       <c r="P32" t="n">
-        <v>3.721844335530549e-08</v>
+        <v>0.2788170021129932</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.756089639932844e-08</v>
+        <v>0.2813824433966985</v>
       </c>
       <c r="R32" t="n">
-        <v>3.790650041036634e-08</v>
+        <v>0.2839714897293436</v>
       </c>
       <c r="S32" t="n">
-        <v>3.82552843809871e-08</v>
+        <v>0.2865843583048824</v>
       </c>
       <c r="T32" t="n">
-        <v>3.860727757052401e-08</v>
+        <v>0.2892212683157058</v>
       </c>
       <c r="U32" t="n">
-        <v>3.896250950753033e-08</v>
+        <v>0.2918824409710306</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.5356536312849159</v>
+        <v>0.5517979127134721</v>
       </c>
       <c r="B33" t="n">
-        <v>3.111397405216199e-08</v>
+        <v>0.231202704923444</v>
       </c>
       <c r="C33" t="n">
-        <v>3.140025886595971e-08</v>
+        <v>0.2333300391950986</v>
       </c>
       <c r="D33" t="n">
-        <v>3.168917783360975e-08</v>
+        <v>0.2354769474207207</v>
       </c>
       <c r="E33" t="n">
-        <v>3.198075519239676e-08</v>
+        <v>0.2376436097034935</v>
       </c>
       <c r="F33" t="n">
-        <v>3.227501540261664e-08</v>
+        <v>0.2398302078037594</v>
       </c>
       <c r="G33" t="n">
-        <v>3.257198314962851e-08</v>
+        <v>0.2420369251542674</v>
       </c>
       <c r="H33" t="n">
-        <v>3.287168334592553e-08</v>
+        <v>0.244263946875562</v>
       </c>
       <c r="I33" t="n">
-        <v>3.317414113322486e-08</v>
+        <v>0.2465114597915119</v>
       </c>
       <c r="J33" t="n">
-        <v>3.347938188457671e-08</v>
+        <v>0.2487796524449832</v>
       </c>
       <c r="K33" t="n">
-        <v>3.378743120649295e-08</v>
+        <v>0.2510687151136564</v>
       </c>
       <c r="L33" t="n">
-        <v>3.40983149410952e-08</v>
+        <v>0.2533788398259879</v>
       </c>
       <c r="M33" t="n">
-        <v>3.441205916828268e-08</v>
+        <v>0.25571022037732</v>
       </c>
       <c r="N33" t="n">
-        <v>3.472869020792009e-08</v>
+        <v>0.2580630523461376</v>
       </c>
       <c r="O33" t="n">
-        <v>3.504823462204554e-08</v>
+        <v>0.2604375331104761</v>
       </c>
       <c r="P33" t="n">
-        <v>3.537071921709885e-08</v>
+        <v>0.2628338618644779</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.569617104617031e-08</v>
+        <v>0.2652522396351047</v>
       </c>
       <c r="R33" t="n">
-        <v>3.602461741127015e-08</v>
+        <v>0.2676928692989994</v>
       </c>
       <c r="S33" t="n">
-        <v>3.635608586561897e-08</v>
+        <v>0.2701559555995073</v>
       </c>
       <c r="T33" t="n">
-        <v>3.669060421595901e-08</v>
+        <v>0.2726417051638504</v>
       </c>
       <c r="U33" t="n">
-        <v>3.702820052488699e-08</v>
+        <v>0.2751503265204623</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.5559273743016759</v>
+        <v>0.5871347248576851</v>
       </c>
       <c r="B34" t="n">
-        <v>2.948861719869085e-08</v>
+        <v>0.2108943592207088</v>
       </c>
       <c r="C34" t="n">
-        <v>2.975994683564839e-08</v>
+        <v>0.2128348330495829</v>
       </c>
       <c r="D34" t="n">
-        <v>3.003377302140626e-08</v>
+        <v>0.21479316149863</v>
       </c>
       <c r="E34" t="n">
-        <v>3.031011872712231e-08</v>
+        <v>0.2167695088511593</v>
       </c>
       <c r="F34" t="n">
-        <v>3.058900713531579e-08</v>
+        <v>0.2187640409020775</v>
       </c>
       <c r="G34" t="n">
-        <v>3.087046164181211e-08</v>
+        <v>0.2207769249717977</v>
       </c>
       <c r="H34" t="n">
-        <v>3.115450585770556e-08</v>
+        <v>0.2228083299202758</v>
       </c>
       <c r="I34" t="n">
-        <v>3.144116361133999e-08</v>
+        <v>0.224858426161176</v>
       </c>
       <c r="J34" t="n">
-        <v>3.173045895030779e-08</v>
+        <v>0.2269273856761668</v>
       </c>
       <c r="K34" t="n">
-        <v>3.202241614346722e-08</v>
+        <v>0.2290153820293484</v>
       </c>
       <c r="L34" t="n">
-        <v>3.23170596829783e-08</v>
+        <v>0.231122590381813</v>
       </c>
       <c r="M34" t="n">
-        <v>3.261441428635748e-08</v>
+        <v>0.2332491875063388</v>
       </c>
       <c r="N34" t="n">
-        <v>3.291450489855114e-08</v>
+        <v>0.2353953518022198</v>
       </c>
       <c r="O34" t="n">
-        <v>3.321735669402826e-08</v>
+        <v>0.2375612633102312</v>
       </c>
       <c r="P34" t="n">
-        <v>3.35229950788922e-08</v>
+        <v>0.2397471037277329</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.383144569301218e-08</v>
+        <v>0.2419530564239127</v>
       </c>
       <c r="R34" t="n">
-        <v>3.414273441217397e-08</v>
+        <v>0.244179306455168</v>
       </c>
       <c r="S34" t="n">
-        <v>3.445688735025083e-08</v>
+        <v>0.2464260405806313</v>
       </c>
       <c r="T34" t="n">
-        <v>3.4773930861394e-08</v>
+        <v>0.2486934472778361</v>
       </c>
       <c r="U34" t="n">
-        <v>3.509389154224366e-08</v>
+        <v>0.2509817167585294</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.5719329608938541</v>
+        <v>0.6161290322580643</v>
       </c>
       <c r="B35" t="n">
-        <v>2.809545418142984e-08</v>
+        <v>0.1937103743953177</v>
       </c>
       <c r="C35" t="n">
-        <v>2.83539650953815e-08</v>
+        <v>0.195492735541839</v>
       </c>
       <c r="D35" t="n">
-        <v>2.861485461094609e-08</v>
+        <v>0.1972914964876305</v>
       </c>
       <c r="E35" t="n">
-        <v>2.887814461402989e-08</v>
+        <v>0.1991068081299537</v>
       </c>
       <c r="F35" t="n">
-        <v>2.914385719191501e-08</v>
+        <v>0.2009388227545008</v>
       </c>
       <c r="G35" t="n">
-        <v>2.941201463511229e-08</v>
+        <v>0.2027876940481697</v>
       </c>
       <c r="H35" t="n">
-        <v>2.968263943923124e-08</v>
+        <v>0.204653577111957</v>
       </c>
       <c r="I35" t="n">
-        <v>2.99557543068672e-08</v>
+        <v>0.2065366284739691</v>
       </c>
       <c r="J35" t="n">
-        <v>3.023138214950581e-08</v>
+        <v>0.2084370061025532</v>
       </c>
       <c r="K35" t="n">
-        <v>3.050954608944511e-08</v>
+        <v>0.2103548694195496</v>
       </c>
       <c r="L35" t="n">
-        <v>3.07902694617352e-08</v>
+        <v>0.2122903793136652</v>
       </c>
       <c r="M35" t="n">
-        <v>3.107357581613583e-08</v>
+        <v>0.2142436981539705</v>
       </c>
       <c r="N35" t="n">
-        <v>3.135948891909199e-08</v>
+        <v>0.2162149898035204</v>
       </c>
       <c r="O35" t="n">
-        <v>3.164803275572767e-08</v>
+        <v>0.2182044196331012</v>
       </c>
       <c r="P35" t="n">
-        <v>3.193923153185789e-08</v>
+        <v>0.2202121545351028</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.223310967601943e-08</v>
+        <v>0.2222383629375198</v>
       </c>
       <c r="R35" t="n">
-        <v>3.252969184152004e-08</v>
+        <v>0.2242832148180802</v>
       </c>
       <c r="S35" t="n">
-        <v>3.282900290850665e-08</v>
+        <v>0.2263468817185057</v>
       </c>
       <c r="T35" t="n">
-        <v>3.313106798605251e-08</v>
+        <v>0.2284295367589013</v>
       </c>
       <c r="U35" t="n">
-        <v>3.34359124142636e-08</v>
+        <v>0.2305313546522788</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.5911396648044689</v>
+        <v>0.6360626185958244</v>
       </c>
       <c r="B36" t="n">
-        <v>2.693448500037904e-08</v>
+        <v>0.1858994722019581</v>
       </c>
       <c r="C36" t="n">
-        <v>2.718231364515915e-08</v>
+        <v>0.1876099639474101</v>
       </c>
       <c r="D36" t="n">
-        <v>2.743242260222933e-08</v>
+        <v>0.1893361942099036</v>
       </c>
       <c r="E36" t="n">
-        <v>2.768483285311959e-08</v>
+        <v>0.1910783078021331</v>
       </c>
       <c r="F36" t="n">
-        <v>2.793956557241441e-08</v>
+        <v>0.1928364508692387</v>
       </c>
       <c r="G36" t="n">
-        <v>2.819664212952916e-08</v>
+        <v>0.1946107709010661</v>
       </c>
       <c r="H36" t="n">
-        <v>2.84560840905027e-08</v>
+        <v>0.1964014167445394</v>
       </c>
       <c r="I36" t="n">
-        <v>2.87179132198066e-08</v>
+        <v>0.1982085386161478</v>
       </c>
       <c r="J36" t="n">
-        <v>2.898215148217089e-08</v>
+        <v>0.2000322881145471</v>
       </c>
       <c r="K36" t="n">
-        <v>2.924882104442674e-08</v>
+        <v>0.2018728182332775</v>
       </c>
       <c r="L36" t="n">
-        <v>2.9517944277366e-08</v>
+        <v>0.2037302833735981</v>
       </c>
       <c r="M36" t="n">
-        <v>2.978954375761785e-08</v>
+        <v>0.2056048393574395</v>
       </c>
       <c r="N36" t="n">
-        <v>3.006364226954277e-08</v>
+        <v>0.2074966434404752</v>
       </c>
       <c r="O36" t="n">
-        <v>3.034026280714391e-08</v>
+        <v>0.2094058543253149</v>
       </c>
       <c r="P36" t="n">
-        <v>3.061942857599602e-08</v>
+        <v>0.2113326321748165</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.090116299519221e-08</v>
+        <v>0.2132771386255231</v>
       </c>
       <c r="R36" t="n">
-        <v>3.118548969930849e-08</v>
+        <v>0.2152395368012222</v>
       </c>
       <c r="S36" t="n">
-        <v>3.147243254038658e-08</v>
+        <v>0.2172199913266305</v>
       </c>
       <c r="T36" t="n">
-        <v>3.176201558993467e-08</v>
+        <v>0.2192186683412037</v>
       </c>
       <c r="U36" t="n">
-        <v>3.205426314094695e-08</v>
+        <v>0.2212357355130741</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.6071452513966484</v>
+        <v>0.6578083491461097</v>
       </c>
       <c r="B37" t="n">
-        <v>2.577351581932825e-08</v>
+        <v>0.1812129308859428</v>
       </c>
       <c r="C37" t="n">
-        <v>2.60106621949368e-08</v>
+        <v>0.1828803009907531</v>
       </c>
       <c r="D37" t="n">
-        <v>2.624999059351258e-08</v>
+        <v>0.1845630128432677</v>
       </c>
       <c r="E37" t="n">
-        <v>2.649152109220929e-08</v>
+        <v>0.186261207605441</v>
       </c>
       <c r="F37" t="n">
-        <v>2.673527395291382e-08</v>
+        <v>0.1879750277380818</v>
       </c>
       <c r="G37" t="n">
-        <v>2.698126962394604e-08</v>
+        <v>0.1897046170128044</v>
       </c>
       <c r="H37" t="n">
-        <v>2.722952874177417e-08</v>
+        <v>0.1914501205240893</v>
       </c>
       <c r="I37" t="n">
-        <v>2.7480072132746e-08</v>
+        <v>0.1932116847014554</v>
       </c>
       <c r="J37" t="n">
-        <v>2.773292081483597e-08</v>
+        <v>0.1949894573217438</v>
       </c>
       <c r="K37" t="n">
-        <v>2.798809599940838e-08</v>
+        <v>0.1967835875215146</v>
       </c>
       <c r="L37" t="n">
-        <v>2.824561909299681e-08</v>
+        <v>0.1985942258095583</v>
       </c>
       <c r="M37" t="n">
-        <v>2.850551169909987e-08</v>
+        <v>0.2004215240795212</v>
       </c>
       <c r="N37" t="n">
-        <v>2.876779561999354e-08</v>
+        <v>0.2022656356226486</v>
       </c>
       <c r="O37" t="n">
-        <v>2.903249285856016e-08</v>
+        <v>0.2041267151406436</v>
       </c>
       <c r="P37" t="n">
-        <v>2.929962562013416e-08</v>
+        <v>0.206004918758645</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9569216314365e-08</v>
+        <v>0.2079004040383254</v>
       </c>
       <c r="R37" t="n">
-        <v>2.984128755709696e-08</v>
+        <v>0.2098133299911078</v>
       </c>
       <c r="S37" t="n">
-        <v>3.01158621722665e-08</v>
+        <v>0.2117438570915059</v>
       </c>
       <c r="T37" t="n">
-        <v>3.039296319381683e-08</v>
+        <v>0.2136921472905856</v>
       </c>
       <c r="U37" t="n">
-        <v>3.067261386763031e-08</v>
+        <v>0.2156583640295517</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.6210167597765365</v>
+        <v>0.6877087286527513</v>
       </c>
       <c r="B38" t="n">
-        <v>2.484474047448757e-08</v>
+        <v>0.1780885700085986</v>
       </c>
       <c r="C38" t="n">
-        <v>2.507334103475888e-08</v>
+        <v>0.1797271923529812</v>
       </c>
       <c r="D38" t="n">
-        <v>2.530404498653913e-08</v>
+        <v>0.1813808919321765</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5536871683481e-08</v>
+        <v>0.1830498074743124</v>
       </c>
       <c r="F38" t="n">
-        <v>2.57718406573133e-08</v>
+        <v>0.1847340789839766</v>
       </c>
       <c r="G38" t="n">
-        <v>2.600897161947949e-08</v>
+        <v>0.1864338477539626</v>
       </c>
       <c r="H38" t="n">
-        <v>2.624828446279129e-08</v>
+        <v>0.1881492563771219</v>
       </c>
       <c r="I38" t="n">
-        <v>2.648979926309747e-08</v>
+        <v>0.1898804487583265</v>
       </c>
       <c r="J38" t="n">
-        <v>2.673353628096798e-08</v>
+        <v>0.191627570126541</v>
       </c>
       <c r="K38" t="n">
-        <v>2.697951596339364e-08</v>
+        <v>0.1933907670470054</v>
       </c>
       <c r="L38" t="n">
-        <v>2.72277589455014e-08</v>
+        <v>0.1951701874335311</v>
       </c>
       <c r="M38" t="n">
-        <v>2.747828605228544e-08</v>
+        <v>0.1969659805609084</v>
       </c>
       <c r="N38" t="n">
-        <v>2.773111830035411e-08</v>
+        <v>0.1987782970774301</v>
       </c>
       <c r="O38" t="n">
-        <v>2.79862768996931e-08</v>
+        <v>0.2006072890175287</v>
       </c>
       <c r="P38" t="n">
-        <v>2.824378325544461e-08</v>
+        <v>0.2024531098145301</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.850365896970316e-08</v>
+        <v>0.2043159143135264</v>
       </c>
       <c r="R38" t="n">
-        <v>2.876592584332766e-08</v>
+        <v>0.2061958587843642</v>
       </c>
       <c r="S38" t="n">
-        <v>2.903060587777038e-08</v>
+        <v>0.2080931009347554</v>
       </c>
       <c r="T38" t="n">
-        <v>2.929772127692251e-08</v>
+        <v>0.2100077999235062</v>
       </c>
       <c r="U38" t="n">
-        <v>2.956729444897694e-08</v>
+        <v>0.2119401163738694</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.6434245810055867</v>
+        <v>0.7148908918406067</v>
       </c>
       <c r="B39" t="n">
-        <v>2.391596512964689e-08</v>
+        <v>0.1796507504472707</v>
       </c>
       <c r="C39" t="n">
-        <v>2.413601987458095e-08</v>
+        <v>0.1813037466718672</v>
       </c>
       <c r="D39" t="n">
-        <v>2.435809937956568e-08</v>
+        <v>0.1829719523877222</v>
       </c>
       <c r="E39" t="n">
-        <v>2.458222227475272e-08</v>
+        <v>0.1846555075398768</v>
       </c>
       <c r="F39" t="n">
-        <v>2.480840736171278e-08</v>
+        <v>0.1863545533610292</v>
       </c>
       <c r="G39" t="n">
-        <v>2.503667361501294e-08</v>
+        <v>0.1880692323833835</v>
       </c>
       <c r="H39" t="n">
-        <v>2.526704018380842e-08</v>
+        <v>0.1897996884506056</v>
       </c>
       <c r="I39" t="n">
-        <v>2.549952639344894e-08</v>
+        <v>0.191546066729891</v>
       </c>
       <c r="J39" t="n">
-        <v>2.573415174709999e-08</v>
+        <v>0.1933085137241424</v>
       </c>
       <c r="K39" t="n">
-        <v>2.59709359273789e-08</v>
+        <v>0.19508717728426</v>
       </c>
       <c r="L39" t="n">
-        <v>2.6209898798006e-08</v>
+        <v>0.1968822066215447</v>
       </c>
       <c r="M39" t="n">
-        <v>2.6451060405471e-08</v>
+        <v>0.1986937523202149</v>
       </c>
       <c r="N39" t="n">
-        <v>2.669444098071467e-08</v>
+        <v>0.2005219663500394</v>
       </c>
       <c r="O39" t="n">
-        <v>2.694006094082604e-08</v>
+        <v>0.2023670020790861</v>
       </c>
       <c r="P39" t="n">
-        <v>2.718794089075506e-08</v>
+        <v>0.2042290142865876</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.743810162504134e-08</v>
+        <v>0.2061081591759259</v>
       </c>
       <c r="R39" t="n">
-        <v>2.769056412955838e-08</v>
+        <v>0.208004594387736</v>
       </c>
       <c r="S39" t="n">
-        <v>2.794534958327426e-08</v>
+        <v>0.2099184790131307</v>
       </c>
       <c r="T39" t="n">
-        <v>2.820247936002818e-08</v>
+        <v>0.2118499736070459</v>
       </c>
       <c r="U39" t="n">
-        <v>2.846197503032357e-08</v>
+        <v>0.2137992402017106</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.6604972067039113</v>
+        <v>0.7529459203036047</v>
       </c>
       <c r="B40" t="n">
-        <v>2.29871897848062e-08</v>
+        <v>0.1796507504472707</v>
       </c>
       <c r="C40" t="n">
-        <v>2.319869871440303e-08</v>
+        <v>0.1813037466718672</v>
       </c>
       <c r="D40" t="n">
-        <v>2.341215377259223e-08</v>
+        <v>0.1829719523877222</v>
       </c>
       <c r="E40" t="n">
-        <v>2.362757286602443e-08</v>
+        <v>0.1846555075398768</v>
       </c>
       <c r="F40" t="n">
-        <v>2.384497406611226e-08</v>
+        <v>0.1863545533610292</v>
       </c>
       <c r="G40" t="n">
-        <v>2.406437561054639e-08</v>
+        <v>0.1880692323833835</v>
       </c>
       <c r="H40" t="n">
-        <v>2.428579590482554e-08</v>
+        <v>0.1897996884506056</v>
       </c>
       <c r="I40" t="n">
-        <v>2.450925352380041e-08</v>
+        <v>0.191546066729891</v>
       </c>
       <c r="J40" t="n">
-        <v>2.473476721323201e-08</v>
+        <v>0.1933085137241424</v>
       </c>
       <c r="K40" t="n">
-        <v>2.496235589136416e-08</v>
+        <v>0.19508717728426</v>
       </c>
       <c r="L40" t="n">
-        <v>2.519203865051059e-08</v>
+        <v>0.1968822066215447</v>
       </c>
       <c r="M40" t="n">
-        <v>2.542383475865657e-08</v>
+        <v>0.1986937523202149</v>
       </c>
       <c r="N40" t="n">
-        <v>2.565776366107525e-08</v>
+        <v>0.2005219663500394</v>
       </c>
       <c r="O40" t="n">
-        <v>2.589384498195898e-08</v>
+        <v>0.2023670020790861</v>
       </c>
       <c r="P40" t="n">
-        <v>2.613209852606552e-08</v>
+        <v>0.2042290142865876</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.637254428037951e-08</v>
+        <v>0.2061081591759259</v>
       </c>
       <c r="R40" t="n">
-        <v>2.66152024157891e-08</v>
+        <v>0.208004594387736</v>
       </c>
       <c r="S40" t="n">
-        <v>2.686009328877815e-08</v>
+        <v>0.2099184790131307</v>
       </c>
       <c r="T40" t="n">
-        <v>2.710723744313385e-08</v>
+        <v>0.2118499736070459</v>
       </c>
       <c r="U40" t="n">
-        <v>2.73566556116702e-08</v>
+        <v>0.2137992402017106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.6743687150837994</v>
+        <v>0.7946252371916502</v>
       </c>
       <c r="B41" t="n">
-        <v>2.27549959485961e-08</v>
+        <v>0.1780885700085986</v>
       </c>
       <c r="C41" t="n">
-        <v>2.29643684243586e-08</v>
+        <v>0.1797271923529812</v>
       </c>
       <c r="D41" t="n">
-        <v>2.317566737084893e-08</v>
+        <v>0.1813808919321765</v>
       </c>
       <c r="E41" t="n">
-        <v>2.338891051384242e-08</v>
+        <v>0.1830498074743124</v>
       </c>
       <c r="F41" t="n">
-        <v>2.360411574221219e-08</v>
+        <v>0.1847340789839766</v>
       </c>
       <c r="G41" t="n">
-        <v>2.382130110942982e-08</v>
+        <v>0.1864338477539626</v>
       </c>
       <c r="H41" t="n">
-        <v>2.404048483507988e-08</v>
+        <v>0.1881492563771219</v>
       </c>
       <c r="I41" t="n">
-        <v>2.426168530638835e-08</v>
+        <v>0.1898804487583265</v>
       </c>
       <c r="J41" t="n">
-        <v>2.448492107976507e-08</v>
+        <v>0.191627570126541</v>
       </c>
       <c r="K41" t="n">
-        <v>2.471021088236054e-08</v>
+        <v>0.1933907670470054</v>
       </c>
       <c r="L41" t="n">
-        <v>2.493757361363681e-08</v>
+        <v>0.1951701874335311</v>
       </c>
       <c r="M41" t="n">
-        <v>2.516702834695303e-08</v>
+        <v>0.1969659805609084</v>
       </c>
       <c r="N41" t="n">
-        <v>2.539859433116545e-08</v>
+        <v>0.1987782970774301</v>
       </c>
       <c r="O41" t="n">
-        <v>2.563229099224228e-08</v>
+        <v>0.2006072890175287</v>
       </c>
       <c r="P41" t="n">
-        <v>2.58681379348932e-08</v>
+        <v>0.2024531098145301</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.610615494421412e-08</v>
+        <v>0.2043159143135264</v>
       </c>
       <c r="R41" t="n">
-        <v>2.634636198734684e-08</v>
+        <v>0.2061958587843642</v>
       </c>
       <c r="S41" t="n">
-        <v>2.658877921515419e-08</v>
+        <v>0.2080931009347554</v>
       </c>
       <c r="T41" t="n">
-        <v>2.683342696391034e-08</v>
+        <v>0.2100077999235062</v>
       </c>
       <c r="U41" t="n">
-        <v>2.708032575700692e-08</v>
+        <v>0.2119401163738694</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.6882402234636873</v>
+        <v>0.8163709677419355</v>
       </c>
       <c r="B42" t="n">
-        <v>2.252280211238598e-08</v>
+        <v>0.1765263895699265</v>
       </c>
       <c r="C42" t="n">
-        <v>2.273003813431417e-08</v>
+        <v>0.1781506380340952</v>
       </c>
       <c r="D42" t="n">
-        <v>2.293918096910562e-08</v>
+        <v>0.179789831476631</v>
       </c>
       <c r="E42" t="n">
-        <v>2.315024816166041e-08</v>
+        <v>0.1814441074087481</v>
       </c>
       <c r="F42" t="n">
-        <v>2.336325741831211e-08</v>
+        <v>0.1831136046069241</v>
       </c>
       <c r="G42" t="n">
-        <v>2.357822660831324e-08</v>
+        <v>0.1847984631245417</v>
       </c>
       <c r="H42" t="n">
-        <v>2.379517376533422e-08</v>
+        <v>0.1864988243036382</v>
       </c>
       <c r="I42" t="n">
-        <v>2.401411708897627e-08</v>
+        <v>0.1882148307867621</v>
       </c>
       <c r="J42" t="n">
-        <v>2.423507494629814e-08</v>
+        <v>0.1899466265289395</v>
       </c>
       <c r="K42" t="n">
-        <v>2.445806587335691e-08</v>
+        <v>0.1916943568097508</v>
       </c>
       <c r="L42" t="n">
-        <v>2.468310857676301e-08</v>
+        <v>0.1934581682455174</v>
       </c>
       <c r="M42" t="n">
-        <v>2.491022193524948e-08</v>
+        <v>0.1952382088016021</v>
       </c>
       <c r="N42" t="n">
-        <v>2.513942500125565e-08</v>
+        <v>0.1970346278048209</v>
       </c>
       <c r="O42" t="n">
-        <v>2.537073700252558e-08</v>
+        <v>0.1988475759559712</v>
       </c>
       <c r="P42" t="n">
-        <v>2.560417734372088e-08</v>
+        <v>0.2006772053424727</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.583976560804873e-08</v>
+        <v>0.2025236694511268</v>
       </c>
       <c r="R42" t="n">
-        <v>2.607752155890459e-08</v>
+        <v>0.2043871231809924</v>
       </c>
       <c r="S42" t="n">
-        <v>2.631746514153022e-08</v>
+        <v>0.2062677228563801</v>
       </c>
       <c r="T42" t="n">
-        <v>2.655961648468682e-08</v>
+        <v>0.2081656262399665</v>
       </c>
       <c r="U42" t="n">
-        <v>2.680399590234364e-08</v>
+        <v>0.2100809925460282</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.7149162011173192</v>
+        <v>0.8444592030360523</v>
       </c>
       <c r="B43" t="n">
-        <v>2.252280211238598e-08</v>
+        <v>0.168715487376567</v>
       </c>
       <c r="C43" t="n">
-        <v>2.273003813431417e-08</v>
+        <v>0.1702678664396663</v>
       </c>
       <c r="D43" t="n">
-        <v>2.293918096910562e-08</v>
+        <v>0.171834529198904</v>
       </c>
       <c r="E43" t="n">
-        <v>2.315024816166041e-08</v>
+        <v>0.1734156070809275</v>
       </c>
       <c r="F43" t="n">
-        <v>2.336325741831211e-08</v>
+        <v>0.175011232721662</v>
       </c>
       <c r="G43" t="n">
-        <v>2.357822660831324e-08</v>
+        <v>0.1766215399774382</v>
       </c>
       <c r="H43" t="n">
-        <v>2.379517376533422e-08</v>
+        <v>0.1782466639362207</v>
       </c>
       <c r="I43" t="n">
-        <v>2.401411708897627e-08</v>
+        <v>0.1798867409289408</v>
       </c>
       <c r="J43" t="n">
-        <v>2.423507494629814e-08</v>
+        <v>0.1815419085409335</v>
       </c>
       <c r="K43" t="n">
-        <v>2.445806587335691e-08</v>
+        <v>0.1832123056234787</v>
       </c>
       <c r="L43" t="n">
-        <v>2.468310857676301e-08</v>
+        <v>0.1848980723054504</v>
       </c>
       <c r="M43" t="n">
-        <v>2.491022193524948e-08</v>
+        <v>0.1865993500050711</v>
       </c>
       <c r="N43" t="n">
-        <v>2.513942500125565e-08</v>
+        <v>0.1883162814417759</v>
       </c>
       <c r="O43" t="n">
-        <v>2.537073700252558e-08</v>
+        <v>0.190049010648185</v>
       </c>
       <c r="P43" t="n">
-        <v>2.560417734372088e-08</v>
+        <v>0.1917976829821863</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.583976560804873e-08</v>
+        <v>0.1935624451391302</v>
       </c>
       <c r="R43" t="n">
-        <v>2.607752155890459e-08</v>
+        <v>0.1953434451641344</v>
       </c>
       <c r="S43" t="n">
-        <v>2.631746514153022e-08</v>
+        <v>0.197140832464505</v>
       </c>
       <c r="T43" t="n">
-        <v>2.655961648468682e-08</v>
+        <v>0.1989547578222689</v>
       </c>
       <c r="U43" t="n">
-        <v>2.680399590234364e-08</v>
+        <v>0.2007853734068235</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.7373240223463695</v>
+        <v>0.8825142314990502</v>
       </c>
       <c r="B44" t="n">
-        <v>2.252280211238598e-08</v>
+        <v>0.1546558634285201</v>
       </c>
       <c r="C44" t="n">
-        <v>2.273003813431417e-08</v>
+        <v>0.1560788775696944</v>
       </c>
       <c r="D44" t="n">
-        <v>2.293918096910562e-08</v>
+        <v>0.1575149850989957</v>
       </c>
       <c r="E44" t="n">
-        <v>2.315024816166041e-08</v>
+        <v>0.1589643064908505</v>
       </c>
       <c r="F44" t="n">
-        <v>2.336325741831211e-08</v>
+        <v>0.1604269633281905</v>
       </c>
       <c r="G44" t="n">
-        <v>2.357822660831324e-08</v>
+        <v>0.161903078312652</v>
       </c>
       <c r="H44" t="n">
-        <v>2.379517376533422e-08</v>
+        <v>0.1633927752748693</v>
       </c>
       <c r="I44" t="n">
-        <v>2.401411708897627e-08</v>
+        <v>0.1648961791848627</v>
       </c>
       <c r="J44" t="n">
-        <v>2.423507494629814e-08</v>
+        <v>0.1664134161625227</v>
       </c>
       <c r="K44" t="n">
-        <v>2.445806587335691e-08</v>
+        <v>0.1679446134881892</v>
       </c>
       <c r="L44" t="n">
-        <v>2.468310857676301e-08</v>
+        <v>0.1694898996133298</v>
       </c>
       <c r="M44" t="n">
-        <v>2.491022193524948e-08</v>
+        <v>0.1710494041713155</v>
       </c>
       <c r="N44" t="n">
-        <v>2.513942500125565e-08</v>
+        <v>0.1726232579882949</v>
       </c>
       <c r="O44" t="n">
-        <v>2.537073700252558e-08</v>
+        <v>0.1742115930941699</v>
       </c>
       <c r="P44" t="n">
-        <v>2.560417734372088e-08</v>
+        <v>0.1758145427336711</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.583976560804873e-08</v>
+        <v>0.1774322413775363</v>
       </c>
       <c r="R44" t="n">
-        <v>2.607752155890459e-08</v>
+        <v>0.1790648247337902</v>
       </c>
       <c r="S44" t="n">
-        <v>2.631746514153022e-08</v>
+        <v>0.1807124297591299</v>
       </c>
       <c r="T44" t="n">
-        <v>2.655961648468682e-08</v>
+        <v>0.1823751946704135</v>
       </c>
       <c r="U44" t="n">
-        <v>2.680399590234364e-08</v>
+        <v>0.1840532589562553</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.7543966480446928</v>
+        <v>0.9051660341555968</v>
       </c>
       <c r="B45" t="n">
-        <v>2.252280211238598e-08</v>
+        <v>0.1484071416738317</v>
       </c>
       <c r="C45" t="n">
-        <v>2.273003813431417e-08</v>
+        <v>0.1497726602941506</v>
       </c>
       <c r="D45" t="n">
-        <v>2.293918096910562e-08</v>
+        <v>0.1511507432768134</v>
       </c>
       <c r="E45" t="n">
-        <v>2.315024816166041e-08</v>
+        <v>0.1525415062285932</v>
       </c>
       <c r="F45" t="n">
-        <v>2.336325741831211e-08</v>
+        <v>0.1539450658199801</v>
       </c>
       <c r="G45" t="n">
-        <v>2.357822660831324e-08</v>
+        <v>0.1553615397949684</v>
       </c>
       <c r="H45" t="n">
-        <v>2.379517376533422e-08</v>
+        <v>0.1567910469809345</v>
       </c>
       <c r="I45" t="n">
-        <v>2.401411708897627e-08</v>
+        <v>0.158233707298605</v>
       </c>
       <c r="J45" t="n">
-        <v>2.423507494629814e-08</v>
+        <v>0.159689641772117</v>
       </c>
       <c r="K45" t="n">
-        <v>2.445806587335691e-08</v>
+        <v>0.1611589725391707</v>
       </c>
       <c r="L45" t="n">
-        <v>2.468310857676301e-08</v>
+        <v>0.1626418228612754</v>
       </c>
       <c r="M45" t="n">
-        <v>2.491022193524948e-08</v>
+        <v>0.1641383171340899</v>
       </c>
       <c r="N45" t="n">
-        <v>2.513942500125565e-08</v>
+        <v>0.165648580897858</v>
       </c>
       <c r="O45" t="n">
-        <v>2.537073700252558e-08</v>
+        <v>0.1671727408479401</v>
       </c>
       <c r="P45" t="n">
-        <v>2.560417734372088e-08</v>
+        <v>0.1687109248454413</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.583976560804873e-08</v>
+        <v>0.1702632619279381</v>
       </c>
       <c r="R45" t="n">
-        <v>2.607752155890459e-08</v>
+        <v>0.171829882320303</v>
       </c>
       <c r="S45" t="n">
-        <v>2.631746514153022e-08</v>
+        <v>0.173410917445629</v>
       </c>
       <c r="T45" t="n">
-        <v>2.655961648468682e-08</v>
+        <v>0.1750064999362547</v>
       </c>
       <c r="U45" t="n">
-        <v>2.680399590234364e-08</v>
+        <v>0.1766167636448907</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.7704022346368723</v>
+        <v>0.9332542694497147</v>
       </c>
       <c r="B46" t="n">
-        <v>2.27549959485961e-08</v>
+        <v>0.1390340590418001</v>
       </c>
       <c r="C46" t="n">
-        <v>2.29643684243586e-08</v>
+        <v>0.1403133343808357</v>
       </c>
       <c r="D46" t="n">
-        <v>2.317566737084893e-08</v>
+        <v>0.1416043805435408</v>
       </c>
       <c r="E46" t="n">
-        <v>2.338891051384242e-08</v>
+        <v>0.1429073058352083</v>
       </c>
       <c r="F46" t="n">
-        <v>2.360411574221219e-08</v>
+        <v>0.1442222195576654</v>
       </c>
       <c r="G46" t="n">
-        <v>2.382130110942982e-08</v>
+        <v>0.1455492320184439</v>
       </c>
       <c r="H46" t="n">
-        <v>2.404048483507988e-08</v>
+        <v>0.1468884545400332</v>
       </c>
       <c r="I46" t="n">
-        <v>2.426168530638835e-08</v>
+        <v>0.1482399994692193</v>
       </c>
       <c r="J46" t="n">
-        <v>2.448492107976507e-08</v>
+        <v>0.1496039801865095</v>
       </c>
       <c r="K46" t="n">
-        <v>2.471021088236054e-08</v>
+        <v>0.150980511115644</v>
       </c>
       <c r="L46" t="n">
-        <v>2.493757361363681e-08</v>
+        <v>0.1523697077331947</v>
       </c>
       <c r="M46" t="n">
-        <v>2.516702834695303e-08</v>
+        <v>0.1537716865782525</v>
       </c>
       <c r="N46" t="n">
-        <v>2.539859433116545e-08</v>
+        <v>0.1551865652622036</v>
       </c>
       <c r="O46" t="n">
-        <v>2.563229099224228e-08</v>
+        <v>0.1566144624785963</v>
       </c>
       <c r="P46" t="n">
-        <v>2.58681379348932e-08</v>
+        <v>0.1580554980130975</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.610615494421412e-08</v>
+        <v>0.1595097927535419</v>
       </c>
       <c r="R46" t="n">
-        <v>2.634636198734684e-08</v>
+        <v>0.1609774687000732</v>
       </c>
       <c r="S46" t="n">
-        <v>2.658877921515419e-08</v>
+        <v>0.1624586489753786</v>
       </c>
       <c r="T46" t="n">
-        <v>2.683342696391034e-08</v>
+        <v>0.1639534578350174</v>
       </c>
       <c r="U46" t="n">
-        <v>2.708032575700692e-08</v>
+        <v>0.1654620206778448</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.7874748603351956</v>
+        <v>0.955</v>
       </c>
       <c r="B47" t="n">
-        <v>2.27549959485961e-08</v>
+        <v>0.1343475177257848</v>
       </c>
       <c r="C47" t="n">
-        <v>2.29643684243586e-08</v>
+        <v>0.1355836714241787</v>
       </c>
       <c r="D47" t="n">
-        <v>2.317566737084893e-08</v>
+        <v>0.136831199176905</v>
       </c>
       <c r="E47" t="n">
-        <v>2.338891051384242e-08</v>
+        <v>0.1380902056385162</v>
       </c>
       <c r="F47" t="n">
-        <v>2.360411574221219e-08</v>
+        <v>0.1393607964265086</v>
       </c>
       <c r="G47" t="n">
-        <v>2.382130110942982e-08</v>
+        <v>0.1406430781301821</v>
       </c>
       <c r="H47" t="n">
-        <v>2.404048483507988e-08</v>
+        <v>0.141937158319583</v>
       </c>
       <c r="I47" t="n">
-        <v>2.426168530638835e-08</v>
+        <v>0.1432431455545269</v>
       </c>
       <c r="J47" t="n">
-        <v>2.448492107976507e-08</v>
+        <v>0.1445611493937062</v>
       </c>
       <c r="K47" t="n">
-        <v>2.471021088236054e-08</v>
+        <v>0.1458912804038811</v>
       </c>
       <c r="L47" t="n">
-        <v>2.493757361363681e-08</v>
+        <v>0.1472336501691549</v>
       </c>
       <c r="M47" t="n">
-        <v>2.516702834695303e-08</v>
+        <v>0.1485883713003343</v>
       </c>
       <c r="N47" t="n">
-        <v>2.539859433116545e-08</v>
+        <v>0.149955557444377</v>
       </c>
       <c r="O47" t="n">
-        <v>2.563229099224228e-08</v>
+        <v>0.151335323293925</v>
       </c>
       <c r="P47" t="n">
-        <v>2.58681379348932e-08</v>
+        <v>0.1527277845969261</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.610615494421412e-08</v>
+        <v>0.1541330581663443</v>
       </c>
       <c r="R47" t="n">
-        <v>2.634636198734684e-08</v>
+        <v>0.1555512618899588</v>
       </c>
       <c r="S47" t="n">
-        <v>2.658877921515419e-08</v>
+        <v>0.1569825147402539</v>
       </c>
       <c r="T47" t="n">
-        <v>2.683342696391034e-08</v>
+        <v>0.1584269367843992</v>
       </c>
       <c r="U47" t="n">
-        <v>2.708032575700692e-08</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>0.8077486033519558</v>
-      </c>
-      <c r="B48" t="n">
-        <v>2.252280211238598e-08</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2.273003813431417e-08</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.293918096910562e-08</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.315024816166041e-08</v>
-      </c>
-      <c r="F48" t="n">
-        <v>2.336325741831211e-08</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.357822660831324e-08</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2.379517376533422e-08</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.401411708897627e-08</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.423507494629814e-08</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.445806587335691e-08</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.468310857676301e-08</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.491022193524948e-08</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.513942500125565e-08</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.537073700252558e-08</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.560417734372088e-08</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.583976560804873e-08</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2.607752155890459e-08</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.631746514153022e-08</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.655961648468682e-08</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.680399590234364e-08</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>0.8269553072625706</v>
-      </c>
-      <c r="B49" t="n">
-        <v>2.205841443996564e-08</v>
-      </c>
-      <c r="C49" t="n">
-        <v>2.226137755422521e-08</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.24662081656189e-08</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.267292345729627e-08</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2.288154077051185e-08</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.309207760607996e-08</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.330455162584279e-08</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.351898065415201e-08</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.373538267936414e-08</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.395377585534954e-08</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.417417850301531e-08</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.439660911184226e-08</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.462108634143594e-08</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.484762902309205e-08</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.50762561613761e-08</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.530698693571781e-08</v>
-      </c>
-      <c r="R49" t="n">
-        <v>2.553984070201994e-08</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.577483699428217e-08</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.601199552623966e-08</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.625133619301696e-08</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>0.8450949720670389</v>
-      </c>
-      <c r="B50" t="n">
-        <v>2.15940267675453e-08</v>
-      </c>
-      <c r="C50" t="n">
-        <v>2.179271697413625e-08</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.199323536213217e-08</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.219559875293212e-08</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2.239982412271159e-08</v>
-      </c>
-      <c r="G50" t="n">
-        <v>2.260592860384669e-08</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2.281392948635134e-08</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.302384421932774e-08</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.323569041243015e-08</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.344948583734217e-08</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2.366524842926761e-08</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.388299628843504e-08</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.410274768161622e-08</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.432452104365852e-08</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.454833497903133e-08</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.47742082633869e-08</v>
-      </c>
-      <c r="R50" t="n">
-        <v>2.50021598451353e-08</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.523220884703411e-08</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.54643745677925e-08</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2.569867648369027e-08</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>0.8643016759776538</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2.066525142270462e-08</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2.085539581395833e-08</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.104728975515872e-08</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2.124094934420383e-08</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2.143639082711107e-08</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.163363059938015e-08</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.183268520736847e-08</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.203357134967921e-08</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.223630587856216e-08</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2.244090580132743e-08</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.26473882817722e-08</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.285577064162061e-08</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.306607036197679e-08</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.327830508479146e-08</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.349249261434179e-08</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.370865091872508e-08</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.392679813136601e-08</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.414695255253799e-08</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.436913265089817e-08</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.45933570650369e-08</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>0.8803072625698334</v>
-      </c>
-      <c r="B52" t="n">
-        <v>2.020086375028428e-08</v>
-      </c>
-      <c r="C52" t="n">
-        <v>2.038673523386936e-08</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.0574316951672e-08</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2.076362463983969e-08</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.095467417931081e-08</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.114748159714687e-08</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2.134206306787703e-08</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2.153843491485495e-08</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.173661361162817e-08</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2.193661578332006e-08</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.21384582080245e-08</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.234215781821339e-08</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.254773170215708e-08</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.275519710535794e-08</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.296457143199702e-08</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2.317587224639416e-08</v>
-      </c>
-      <c r="R52" t="n">
-        <v>2.338911727448137e-08</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.360432440528993e-08</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.382151169245101e-08</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2.404069735571022e-08</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>0.8973798882681566</v>
-      </c>
-      <c r="B53" t="n">
-        <v>1.92720884054436e-08</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1.944941407369144e-08</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.962837134469855e-08</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1.980897523111141e-08</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.999124088371029e-08</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.017518359268032e-08</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.036081878889416e-08</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.054816204520642e-08</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.073722907776018e-08</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.092803574730532e-08</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2.11205980605291e-08</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.131493217139896e-08</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2.151105438251764e-08</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.170898114649088e-08</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2.190872906730748e-08</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.211031490173234e-08</v>
-      </c>
-      <c r="R53" t="n">
-        <v>2.231375556071209e-08</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.251906811079382e-08</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.272626977555668e-08</v>
-      </c>
-      <c r="U53" t="n">
-        <v>2.293537793705685e-08</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>0.9144525139664814</v>
-      </c>
-      <c r="B54" t="n">
-        <v>1.857550689681315e-08</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1.874642320355805e-08</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.891891213946852e-08</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1.909298817456525e-08</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.926866591200996e-08</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.944596008933047e-08</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.962488557965705e-08</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.980545739297009e-08</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.998769067735925e-08</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.017160072029432e-08</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.03572029499076e-08</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.054451293628819e-08</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.073354639278813e-08</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.092431917734065e-08</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.111684729379037e-08</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2.131114689323603e-08</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.150723427538519e-08</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.170512588992179e-08</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.1904838337886e-08</v>
-      </c>
-      <c r="U54" t="n">
-        <v>2.210638837306688e-08</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>0.9325921787709497</v>
-      </c>
-      <c r="B55" t="n">
-        <v>1.787892538818258e-08</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1.804343233342455e-08</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.820945293423838e-08</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1.837700111801898e-08</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.854609094030951e-08</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.871673658598051e-08</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.888895237041984e-08</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.906275274073363e-08</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.92381522769582e-08</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1.941516569328321e-08</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.9593807839286e-08</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.977409370117731e-08</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1.99560384030585e-08</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.01396572081903e-08</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.032496552027316e-08</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.051197888473959e-08</v>
-      </c>
-      <c r="R55" t="n">
-        <v>2.070071299005816e-08</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.089118366904964e-08</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.108340690021519e-08</v>
-      </c>
-      <c r="U55" t="n">
-        <v>2.127739880907679e-08</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>0.9550000000000001</v>
-      </c>
-      <c r="B56" t="n">
-        <v>1.695015004334202e-08</v>
-      </c>
-      <c r="C56" t="n">
-        <v>1.710611117324674e-08</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.726350732726504e-08</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1.742235170929081e-08</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.75826576447091e-08</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1.774443858151407e-08</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.790770809143708e-08</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.807247987108522e-08</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.823876774309034e-08</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.840658565726859e-08</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.857594769179071e-08</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.874686805436299e-08</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.891936108341919e-08</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.909344124932336e-08</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.926912315558374e-08</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.944642154007789e-08</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.9625351276289e-08</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.980592737455366e-08</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.998816498332099e-08</v>
-      </c>
-      <c r="U56" t="n">
-        <v>2.017207939042355e-08</v>
+        <v>0.1598846491943224</v>
       </c>
     </row>
   </sheetData>
